--- a/output/freshwater/Europe_freshwater_summary_latest.xlsx
+++ b/output/freshwater/Europe_freshwater_summary_latest.xlsx
@@ -487,14 +487,18 @@
       <c r="B2" t="n">
         <v>2018</v>
       </c>
-      <c r="C2"/>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" t="n">
         <v>3991</v>
       </c>
       <c r="E2" t="n">
         <v>1172</v>
       </c>
-      <c r="F2"/>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
       <c r="G2" t="n">
         <v>26450875</v>
       </c>
@@ -509,14 +513,18 @@
       <c r="B3" t="n">
         <v>2019</v>
       </c>
-      <c r="C3"/>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
       <c r="D3" t="n">
         <v>4250</v>
       </c>
       <c r="E3" t="n">
         <v>1187</v>
       </c>
-      <c r="F3"/>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="n">
         <v>29615585</v>
       </c>
@@ -531,14 +539,18 @@
       <c r="B4" t="n">
         <v>2020</v>
       </c>
-      <c r="C4"/>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
       <c r="D4" t="n">
         <v>4527</v>
       </c>
       <c r="E4" t="n">
         <v>1229</v>
       </c>
-      <c r="F4"/>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" t="n">
         <v>30304621</v>
       </c>
@@ -553,14 +565,18 @@
       <c r="B5" t="n">
         <v>2021</v>
       </c>
-      <c r="C5"/>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
       <c r="D5" t="n">
         <v>4875</v>
       </c>
       <c r="E5" t="n">
         <v>1261</v>
       </c>
-      <c r="F5"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" t="n">
         <v>33034220</v>
       </c>
@@ -575,14 +591,18 @@
       <c r="B6" t="n">
         <v>2022</v>
       </c>
-      <c r="C6"/>
+      <c r="C6" t="n">
+        <v>9437</v>
+      </c>
       <c r="D6" t="n">
         <v>4696</v>
       </c>
       <c r="E6" t="n">
         <v>1131</v>
       </c>
-      <c r="F6"/>
+      <c r="F6" t="n">
+        <v>75269793</v>
+      </c>
       <c r="G6" t="n">
         <v>32152739</v>
       </c>
@@ -597,14 +617,18 @@
       <c r="B7" t="n">
         <v>2023</v>
       </c>
-      <c r="C7"/>
+      <c r="C7" t="n">
+        <v>10340</v>
+      </c>
       <c r="D7" t="n">
         <v>5141</v>
       </c>
       <c r="E7" t="n">
         <v>1207</v>
       </c>
-      <c r="F7"/>
+      <c r="F7" t="n">
+        <v>88436183</v>
+      </c>
       <c r="G7" t="n">
         <v>36915749</v>
       </c>
@@ -614,46 +638,42 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C8"/>
-      <c r="D8" t="n">
-        <v>111</v>
-      </c>
-      <c r="E8" t="n">
-        <v>111</v>
-      </c>
-      <c r="F8"/>
-      <c r="G8" t="n">
-        <v>842600</v>
-      </c>
-      <c r="H8" t="n">
-        <v>841000</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C8" t="n">
+        <v>10016</v>
+      </c>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8" t="n">
+        <v>81022074</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E9" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="F9"/>
       <c r="G9" t="n">
-        <v>538193</v>
+        <v>842600</v>
       </c>
       <c r="H9" t="n">
-        <v>538347</v>
+        <v>841000</v>
       </c>
     </row>
     <row r="10">
@@ -661,21 +681,21 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>86</v>
       </c>
       <c r="E10" t="n">
-        <v>209</v>
+        <v>86</v>
       </c>
       <c r="F10"/>
       <c r="G10" t="n">
-        <v>1396409</v>
+        <v>538193</v>
       </c>
       <c r="H10" t="n">
-        <v>1394030</v>
+        <v>538347</v>
       </c>
     </row>
     <row r="11">
@@ -683,21 +703,21 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="E11" t="n">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="F11"/>
       <c r="G11" t="n">
-        <v>1446425</v>
+        <v>1396409</v>
       </c>
       <c r="H11" t="n">
-        <v>1447320</v>
+        <v>1394030</v>
       </c>
     </row>
     <row r="12">
@@ -705,21 +725,21 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="n">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="E12" t="n">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="F12"/>
       <c r="G12" t="n">
-        <v>1740569</v>
+        <v>1446425</v>
       </c>
       <c r="H12" t="n">
-        <v>1739960</v>
+        <v>1447320</v>
       </c>
     </row>
     <row r="13">
@@ -727,43 +747,43 @@
         <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="E13" t="n">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="F13"/>
       <c r="G13" t="n">
-        <v>1830557</v>
+        <v>1740569</v>
       </c>
       <c r="H13" t="n">
-        <v>1832170</v>
+        <v>1739960</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="n">
-        <v>11239</v>
+        <v>261</v>
       </c>
       <c r="E14" t="n">
-        <v>4375</v>
+        <v>261</v>
       </c>
       <c r="F14"/>
       <c r="G14" t="n">
-        <v>30771990</v>
+        <v>1830557</v>
       </c>
       <c r="H14" t="n">
-        <v>9068000</v>
+        <v>1832170</v>
       </c>
     </row>
     <row r="15">
@@ -771,21 +791,25 @@
         <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C15"/>
+        <v>2018</v>
+      </c>
+      <c r="C15" t="n">
+        <v>18465</v>
+      </c>
       <c r="D15" t="n">
-        <v>11119</v>
+        <v>11239</v>
       </c>
       <c r="E15" t="n">
-        <v>5362</v>
-      </c>
-      <c r="F15"/>
+        <v>4375</v>
+      </c>
+      <c r="F15" t="n">
+        <v>56410221</v>
+      </c>
       <c r="G15" t="n">
-        <v>30359427</v>
+        <v>30771990</v>
       </c>
       <c r="H15" t="n">
-        <v>11106513</v>
+        <v>9068000</v>
       </c>
     </row>
     <row r="16">
@@ -793,21 +817,25 @@
         <v>10</v>
       </c>
       <c r="B16" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C16"/>
+        <v>2019</v>
+      </c>
+      <c r="C16" t="n">
+        <v>18448</v>
+      </c>
       <c r="D16" t="n">
-        <v>10855</v>
+        <v>11119</v>
       </c>
       <c r="E16" t="n">
-        <v>4274</v>
-      </c>
-      <c r="F16"/>
+        <v>5362</v>
+      </c>
+      <c r="F16" t="n">
+        <v>54540885</v>
+      </c>
       <c r="G16" t="n">
-        <v>33175287</v>
+        <v>30359427</v>
       </c>
       <c r="H16" t="n">
-        <v>9283287</v>
+        <v>11106513</v>
       </c>
     </row>
     <row r="17">
@@ -815,21 +843,25 @@
         <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C17"/>
+        <v>2020</v>
+      </c>
+      <c r="C17" t="n">
+        <v>15253</v>
+      </c>
       <c r="D17" t="n">
-        <v>10381</v>
+        <v>10855</v>
       </c>
       <c r="E17" t="n">
-        <v>4284</v>
-      </c>
-      <c r="F17"/>
+        <v>4274</v>
+      </c>
+      <c r="F17" t="n">
+        <v>46552367</v>
+      </c>
       <c r="G17" t="n">
-        <v>33152079</v>
+        <v>33175287</v>
       </c>
       <c r="H17" t="n">
-        <v>10674619</v>
+        <v>9283287</v>
       </c>
     </row>
     <row r="18">
@@ -837,21 +869,25 @@
         <v>10</v>
       </c>
       <c r="B18" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C18"/>
+        <v>2021</v>
+      </c>
+      <c r="C18" t="n">
+        <v>16954</v>
+      </c>
       <c r="D18" t="n">
-        <v>7564</v>
+        <v>10381</v>
       </c>
       <c r="E18" t="n">
-        <v>4150</v>
-      </c>
-      <c r="F18"/>
+        <v>4284</v>
+      </c>
+      <c r="F18" t="n">
+        <v>56259225</v>
+      </c>
       <c r="G18" t="n">
-        <v>28472137</v>
+        <v>33152079</v>
       </c>
       <c r="H18" t="n">
-        <v>12331032</v>
+        <v>10674619</v>
       </c>
     </row>
     <row r="19">
@@ -859,57 +895,69 @@
         <v>10</v>
       </c>
       <c r="B19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C19"/>
+        <v>2022</v>
+      </c>
+      <c r="C19" t="n">
+        <v>15243</v>
+      </c>
       <c r="D19" t="n">
-        <v>8809</v>
+        <v>7564</v>
       </c>
       <c r="E19" t="n">
         <v>4150</v>
       </c>
-      <c r="F19"/>
+      <c r="F19" t="n">
+        <v>57778979</v>
+      </c>
       <c r="G19" t="n">
-        <v>38741262</v>
+        <v>28472137</v>
       </c>
       <c r="H19" t="n">
-        <v>13386660</v>
+        <v>12331032</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C20"/>
+        <v>2023</v>
+      </c>
+      <c r="C20" t="n">
+        <v>17619</v>
+      </c>
       <c r="D20" t="n">
-        <v>1743</v>
-      </c>
-      <c r="E20"/>
-      <c r="F20"/>
+        <v>8809</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4150</v>
+      </c>
+      <c r="F20" t="n">
+        <v>77600472</v>
+      </c>
       <c r="G20" t="n">
-        <v>26109920</v>
-      </c>
-      <c r="H20"/>
+        <v>38741262</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13386660</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C21"/>
-      <c r="D21" t="n">
-        <v>2169</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C21" t="n">
+        <v>19973</v>
+      </c>
+      <c r="D21"/>
       <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21" t="n">
-        <v>33910246</v>
-      </c>
+      <c r="F21" t="n">
+        <v>93137072</v>
+      </c>
+      <c r="G21"/>
       <c r="H21"/>
     </row>
     <row r="22">
@@ -917,16 +965,16 @@
         <v>11</v>
       </c>
       <c r="B22" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="n">
-        <v>2169</v>
+        <v>1743</v>
       </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22" t="n">
-        <v>33302672</v>
+        <v>26109920</v>
       </c>
       <c r="H22"/>
     </row>
@@ -935,16 +983,16 @@
         <v>11</v>
       </c>
       <c r="B23" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="n">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23" t="n">
-        <v>32160700</v>
+        <v>33910246</v>
       </c>
       <c r="H23"/>
     </row>
@@ -953,16 +1001,16 @@
         <v>11</v>
       </c>
       <c r="B24" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="n">
-        <v>2310</v>
+        <v>2169</v>
       </c>
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24" t="n">
-        <v>38741000</v>
+        <v>33302672</v>
       </c>
       <c r="H24"/>
     </row>
@@ -971,83 +1019,79 @@
         <v>11</v>
       </c>
       <c r="B25" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="n">
-        <v>2310</v>
+        <v>2174</v>
       </c>
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25" t="n">
-        <v>37680720</v>
+        <v>32160700</v>
       </c>
       <c r="H25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="n">
-        <v>44</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3</v>
-      </c>
+        <v>2310</v>
+      </c>
+      <c r="E26"/>
       <c r="F26"/>
       <c r="G26" t="n">
-        <v>363975</v>
-      </c>
-      <c r="H26" t="n">
-        <v>55000</v>
-      </c>
+        <v>38741000</v>
+      </c>
+      <c r="H26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="n">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="n">
-        <v>54</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4</v>
-      </c>
+        <v>2310</v>
+      </c>
+      <c r="E27"/>
       <c r="F27"/>
       <c r="G27" t="n">
-        <v>463657</v>
-      </c>
-      <c r="H27" t="n">
-        <v>78800</v>
-      </c>
+        <v>37680720</v>
+      </c>
+      <c r="H27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
         <v>12</v>
       </c>
       <c r="B28" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C28"/>
+        <v>2018</v>
+      </c>
+      <c r="C28" t="n">
+        <v>88</v>
+      </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
       </c>
-      <c r="F28"/>
+      <c r="F28" t="n">
+        <v>725320</v>
+      </c>
       <c r="G28" t="n">
-        <v>308986</v>
+        <v>363975</v>
       </c>
       <c r="H28" t="n">
-        <v>53428</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="29">
@@ -1055,21 +1099,25 @@
         <v>12</v>
       </c>
       <c r="B29" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C29"/>
+        <v>2019</v>
+      </c>
+      <c r="C29" t="n">
+        <v>108</v>
+      </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
-      <c r="F29"/>
+      <c r="F29" t="n">
+        <v>927138</v>
+      </c>
       <c r="G29" t="n">
-        <v>479720</v>
+        <v>463657</v>
       </c>
       <c r="H29" t="n">
-        <v>66000</v>
+        <v>78800</v>
       </c>
     </row>
     <row r="30">
@@ -1077,21 +1125,25 @@
         <v>12</v>
       </c>
       <c r="B30" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C30"/>
+        <v>2020</v>
+      </c>
+      <c r="C30" t="n">
+        <v>71</v>
+      </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30"/>
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>608138</v>
+      </c>
       <c r="G30" t="n">
-        <v>594293</v>
+        <v>308986</v>
       </c>
       <c r="H30" t="n">
-        <v>72432</v>
+        <v>53428</v>
       </c>
     </row>
     <row r="31">
@@ -1099,109 +1151,121 @@
         <v>12</v>
       </c>
       <c r="B31" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C31"/>
+        <v>2021</v>
+      </c>
+      <c r="C31" t="n">
+        <v>112</v>
+      </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31"/>
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>961007</v>
+      </c>
       <c r="G31" t="n">
-        <v>546634</v>
+        <v>479720</v>
       </c>
       <c r="H31" t="n">
-        <v>22370</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C32"/>
+        <v>2022</v>
+      </c>
+      <c r="C32" t="n">
+        <v>139</v>
+      </c>
       <c r="D32" t="n">
-        <v>21751</v>
+        <v>70</v>
       </c>
       <c r="E32" t="n">
-        <v>20639</v>
-      </c>
-      <c r="F32"/>
+        <v>5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1188216</v>
+      </c>
       <c r="G32" t="n">
-        <v>45963873</v>
+        <v>594293</v>
       </c>
       <c r="H32" t="n">
-        <v>43797000</v>
+        <v>72432</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C33"/>
+        <v>2023</v>
+      </c>
+      <c r="C33" t="n">
+        <v>125</v>
+      </c>
       <c r="D33" t="n">
-        <v>20986</v>
+        <v>62</v>
       </c>
       <c r="E33" t="n">
-        <v>20050</v>
-      </c>
-      <c r="F33"/>
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1093820</v>
+      </c>
       <c r="G33" t="n">
-        <v>42173602</v>
+        <v>546634</v>
       </c>
       <c r="H33" t="n">
-        <v>38104830</v>
+        <v>22370</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C34"/>
-      <c r="D34" t="n">
-        <v>20401</v>
-      </c>
-      <c r="E34" t="n">
-        <v>19685</v>
-      </c>
-      <c r="F34"/>
-      <c r="G34" t="n">
-        <v>39973165</v>
-      </c>
-      <c r="H34" t="n">
-        <v>35882009</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C34" t="n">
+        <v>97</v>
+      </c>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34" t="n">
+        <v>923594</v>
+      </c>
+      <c r="G34"/>
+      <c r="H34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
         <v>13</v>
       </c>
       <c r="B35" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C35"/>
+        <v>2018</v>
+      </c>
+      <c r="C35" t="n">
+        <v>43500</v>
+      </c>
       <c r="D35" t="n">
-        <v>20991</v>
+        <v>21751</v>
       </c>
       <c r="E35" t="n">
-        <v>19919</v>
-      </c>
-      <c r="F35"/>
+        <v>20639</v>
+      </c>
+      <c r="F35" t="n">
+        <v>97190002</v>
+      </c>
       <c r="G35" t="n">
-        <v>43480681</v>
+        <v>45963873</v>
       </c>
       <c r="H35" t="n">
-        <v>40282648</v>
+        <v>43797000</v>
       </c>
     </row>
     <row r="36">
@@ -1209,21 +1273,25 @@
         <v>13</v>
       </c>
       <c r="B36" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C36"/>
+        <v>2019</v>
+      </c>
+      <c r="C36" t="n">
+        <v>41978</v>
+      </c>
       <c r="D36" t="n">
-        <v>19259</v>
+        <v>20986</v>
       </c>
       <c r="E36" t="n">
-        <v>18559</v>
-      </c>
-      <c r="F36"/>
+        <v>20050</v>
+      </c>
+      <c r="F36" t="n">
+        <v>82473547</v>
+      </c>
       <c r="G36" t="n">
-        <v>48497446</v>
+        <v>42173602</v>
       </c>
       <c r="H36" t="n">
-        <v>46271844</v>
+        <v>38104830</v>
       </c>
     </row>
     <row r="37">
@@ -1231,131 +1299,147 @@
         <v>13</v>
       </c>
       <c r="B37" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C37"/>
+        <v>2020</v>
+      </c>
+      <c r="C37" t="n">
+        <v>40804</v>
+      </c>
       <c r="D37" t="n">
-        <v>18613</v>
+        <v>20401</v>
       </c>
       <c r="E37" t="n">
-        <v>17954</v>
-      </c>
-      <c r="F37"/>
+        <v>19685</v>
+      </c>
+      <c r="F37" t="n">
+        <v>77886069</v>
+      </c>
       <c r="G37" t="n">
-        <v>53453140</v>
+        <v>39973165</v>
       </c>
       <c r="H37" t="n">
-        <v>47488930</v>
+        <v>35882009</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C38"/>
+        <v>2021</v>
+      </c>
+      <c r="C38" t="n">
+        <v>41982</v>
+      </c>
       <c r="D38" t="n">
-        <v>18252</v>
+        <v>20991</v>
       </c>
       <c r="E38" t="n">
-        <v>7268</v>
-      </c>
-      <c r="F38"/>
+        <v>19919</v>
+      </c>
+      <c r="F38" t="n">
+        <v>89123393</v>
+      </c>
       <c r="G38" t="n">
-        <v>80503725</v>
+        <v>43480681</v>
       </c>
       <c r="H38" t="n">
-        <v>32999000</v>
+        <v>40282648</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C39"/>
+        <v>2022</v>
+      </c>
+      <c r="C39" t="n">
+        <v>38518</v>
+      </c>
       <c r="D39" t="n">
-        <v>18615</v>
+        <v>19259</v>
       </c>
       <c r="E39" t="n">
-        <v>8468</v>
-      </c>
-      <c r="F39"/>
+        <v>18559</v>
+      </c>
+      <c r="F39" t="n">
+        <v>98439920</v>
+      </c>
       <c r="G39" t="n">
-        <v>78542004</v>
+        <v>48497446</v>
       </c>
       <c r="H39" t="n">
-        <v>36709187</v>
+        <v>46271844</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C40"/>
+        <v>2023</v>
+      </c>
+      <c r="C40" t="n">
+        <v>37227</v>
+      </c>
       <c r="D40" t="n">
-        <v>18693</v>
+        <v>18613</v>
       </c>
       <c r="E40" t="n">
-        <v>8276</v>
-      </c>
-      <c r="F40"/>
+        <v>17954</v>
+      </c>
+      <c r="F40" t="n">
+        <v>101233551</v>
+      </c>
       <c r="G40" t="n">
-        <v>85885849</v>
+        <v>53453140</v>
       </c>
       <c r="H40" t="n">
-        <v>34761999</v>
+        <v>47488930</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C41"/>
-      <c r="D41" t="n">
-        <v>18294</v>
-      </c>
-      <c r="E41" t="n">
-        <v>7416</v>
-      </c>
-      <c r="F41"/>
-      <c r="G41" t="n">
-        <v>88670995</v>
-      </c>
-      <c r="H41" t="n">
-        <v>37073390</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C41" t="n">
+        <v>37370</v>
+      </c>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41" t="n">
+        <v>102342779</v>
+      </c>
+      <c r="G41"/>
+      <c r="H41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
         <v>14</v>
       </c>
       <c r="B42" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C42"/>
+        <v>2018</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
       <c r="D42" t="n">
-        <v>17833</v>
+        <v>18252</v>
       </c>
       <c r="E42" t="n">
-        <v>6897</v>
-      </c>
-      <c r="F42"/>
+        <v>7268</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
       <c r="G42" t="n">
-        <v>96524098</v>
+        <v>80503725</v>
       </c>
       <c r="H42" t="n">
-        <v>38961205</v>
+        <v>32999000</v>
       </c>
     </row>
     <row r="43">
@@ -1363,2812 +1447,3812 @@
         <v>14</v>
       </c>
       <c r="B43" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C43"/>
+        <v>2019</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
       <c r="D43" t="n">
-        <v>16848</v>
+        <v>18615</v>
       </c>
       <c r="E43" t="n">
-        <v>6887</v>
-      </c>
-      <c r="F43"/>
+        <v>8468</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
       <c r="G43" t="n">
-        <v>98964660</v>
+        <v>78542004</v>
       </c>
       <c r="H43" t="n">
-        <v>39541060</v>
+        <v>36709187</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B44" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C44"/>
+        <v>2020</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
       <c r="D44" t="n">
-        <v>21384</v>
+        <v>18693</v>
       </c>
       <c r="E44" t="n">
-        <v>810</v>
-      </c>
-      <c r="F44"/>
+        <v>8276</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
       <c r="G44" t="n">
-        <v>76984768</v>
+        <v>85885849</v>
       </c>
       <c r="H44" t="n">
-        <v>7706000</v>
+        <v>34761999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B45" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C45"/>
+        <v>2021</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
       <c r="D45" t="n">
-        <v>23412</v>
+        <v>18294</v>
       </c>
       <c r="E45" t="n">
-        <v>767</v>
-      </c>
-      <c r="F45"/>
+        <v>7416</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
       <c r="G45" t="n">
-        <v>82365636</v>
+        <v>88670995</v>
       </c>
       <c r="H45" t="n">
-        <v>6134246</v>
+        <v>37073390</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B46" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C46"/>
+        <v>2022</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
       <c r="D46" t="n">
-        <v>35046</v>
+        <v>17833</v>
       </c>
       <c r="E46" t="n">
-        <v>1442</v>
-      </c>
-      <c r="F46"/>
+        <v>6897</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
       <c r="G46" t="n">
-        <v>123105289</v>
+        <v>96524098</v>
       </c>
       <c r="H46" t="n">
-        <v>7381528</v>
+        <v>38961205</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B47" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C47"/>
+        <v>2023</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
       <c r="D47" t="n">
-        <v>21446</v>
+        <v>16848</v>
       </c>
       <c r="E47" t="n">
-        <v>1473</v>
-      </c>
-      <c r="F47"/>
+        <v>6887</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
       <c r="G47" t="n">
-        <v>72661585</v>
+        <v>98964660</v>
       </c>
       <c r="H47" t="n">
-        <v>11607429</v>
+        <v>39541060</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B48" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C48"/>
-      <c r="D48" t="n">
-        <v>18204</v>
-      </c>
-      <c r="E48" t="n">
-        <v>3051</v>
-      </c>
-      <c r="F48"/>
-      <c r="G48" t="n">
-        <v>74472013</v>
-      </c>
-      <c r="H48" t="n">
-        <v>15912028</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48"/>
+      <c r="H48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
         <v>15</v>
       </c>
       <c r="B49" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C49"/>
+        <v>2018</v>
+      </c>
+      <c r="C49" t="n">
+        <v>36260</v>
+      </c>
       <c r="D49" t="n">
-        <v>16966</v>
-      </c>
-      <c r="E49"/>
-      <c r="F49"/>
+        <v>21384</v>
+      </c>
+      <c r="E49" t="n">
+        <v>810</v>
+      </c>
+      <c r="F49" t="n">
+        <v>21111776</v>
+      </c>
       <c r="G49" t="n">
-        <v>76445102</v>
-      </c>
-      <c r="H49"/>
+        <v>76984768</v>
+      </c>
+      <c r="H49" t="n">
+        <v>7706000</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B50" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C50"/>
+        <v>2019</v>
+      </c>
+      <c r="C50" t="n">
+        <v>44452</v>
+      </c>
       <c r="D50" t="n">
-        <v>944</v>
+        <v>23412</v>
       </c>
       <c r="E50" t="n">
-        <v>139</v>
-      </c>
-      <c r="F50"/>
+        <v>767</v>
+      </c>
+      <c r="F50" t="n">
+        <v>133339345</v>
+      </c>
       <c r="G50" t="n">
-        <v>4200794</v>
+        <v>82365636</v>
       </c>
       <c r="H50" t="n">
-        <v>872000</v>
+        <v>6134246</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B51" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C51"/>
+        <v>2020</v>
+      </c>
+      <c r="C51" t="n">
+        <v>38552</v>
+      </c>
       <c r="D51" t="n">
-        <v>857</v>
+        <v>35046</v>
       </c>
       <c r="E51" t="n">
-        <v>134</v>
-      </c>
-      <c r="F51"/>
+        <v>1442</v>
+      </c>
+      <c r="F51" t="n">
+        <v>116456597</v>
+      </c>
       <c r="G51" t="n">
-        <v>3180015</v>
+        <v>123105289</v>
       </c>
       <c r="H51" t="n">
-        <v>4175667</v>
+        <v>7381528</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B52" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C52"/>
+        <v>2021</v>
+      </c>
+      <c r="C52" t="n">
+        <v>34167</v>
+      </c>
       <c r="D52" t="n">
-        <v>966</v>
+        <v>21446</v>
       </c>
       <c r="E52" t="n">
-        <v>219</v>
-      </c>
-      <c r="F52"/>
+        <v>1473</v>
+      </c>
+      <c r="F52" t="n">
+        <v>104003334</v>
+      </c>
       <c r="G52" t="n">
-        <v>3810096</v>
+        <v>72661585</v>
       </c>
       <c r="H52" t="n">
-        <v>1339941</v>
+        <v>11607429</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B53" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C53"/>
+        <v>2022</v>
+      </c>
+      <c r="C53" t="n">
+        <v>31836</v>
+      </c>
       <c r="D53" t="n">
-        <v>581</v>
+        <v>18204</v>
       </c>
       <c r="E53" t="n">
-        <v>137</v>
-      </c>
-      <c r="F53"/>
+        <v>3051</v>
+      </c>
+      <c r="F53" t="n">
+        <v>110376607</v>
+      </c>
       <c r="G53" t="n">
-        <v>3012329</v>
+        <v>74472013</v>
       </c>
       <c r="H53" t="n">
-        <v>860829</v>
+        <v>15912028</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B54" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C54"/>
+        <v>2023</v>
+      </c>
+      <c r="C54" t="n">
+        <v>27426</v>
+      </c>
       <c r="D54" t="n">
-        <v>506</v>
-      </c>
-      <c r="E54" t="n">
-        <v>123</v>
-      </c>
-      <c r="F54"/>
+        <v>16966</v>
+      </c>
+      <c r="E54"/>
+      <c r="F54" t="n">
+        <v>100594720</v>
+      </c>
       <c r="G54" t="n">
-        <v>3401976</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1016344</v>
-      </c>
+        <v>76445102</v>
+      </c>
+      <c r="H54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B55" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C55"/>
-      <c r="D55" t="n">
-        <v>643</v>
-      </c>
-      <c r="E55" t="n">
-        <v>133</v>
-      </c>
-      <c r="F55"/>
-      <c r="G55" t="n">
-        <v>4310757</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1194970</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C55" t="n">
+        <v>30194</v>
+      </c>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55" t="n">
+        <v>117640875</v>
+      </c>
+      <c r="G55"/>
+      <c r="H55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56" t="n">
         <v>2018</v>
       </c>
-      <c r="C56"/>
-      <c r="D56"/>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>944</v>
+      </c>
       <c r="E56" t="n">
-        <v>404</v>
-      </c>
-      <c r="F56"/>
-      <c r="G56"/>
+        <v>139</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4200794</v>
+      </c>
       <c r="H56" t="n">
-        <v>2782000</v>
+        <v>872000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" t="n">
         <v>2019</v>
       </c>
-      <c r="C57"/>
-      <c r="D57"/>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>857</v>
+      </c>
       <c r="E57" t="n">
-        <v>398</v>
-      </c>
-      <c r="F57"/>
-      <c r="G57"/>
+        <v>134</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3180015</v>
+      </c>
       <c r="H57" t="n">
-        <v>2676520</v>
+        <v>4175667</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58" t="n">
         <v>2020</v>
       </c>
-      <c r="C58"/>
-      <c r="D58"/>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>966</v>
+      </c>
       <c r="E58" t="n">
-        <v>398</v>
-      </c>
-      <c r="F58"/>
-      <c r="G58"/>
+        <v>219</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>3810096</v>
+      </c>
       <c r="H58" t="n">
-        <v>2617529</v>
+        <v>1339941</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" t="n">
         <v>2021</v>
       </c>
-      <c r="C59"/>
-      <c r="D59"/>
+      <c r="C59" t="n">
+        <v>113</v>
+      </c>
+      <c r="D59" t="n">
+        <v>581</v>
+      </c>
       <c r="E59" t="n">
-        <v>298</v>
-      </c>
-      <c r="F59"/>
-      <c r="G59"/>
+        <v>137</v>
+      </c>
+      <c r="F59" t="n">
+        <v>465943</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3012329</v>
+      </c>
       <c r="H59" t="n">
-        <v>2991065</v>
+        <v>860829</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B60" t="n">
         <v>2022</v>
       </c>
-      <c r="C60"/>
-      <c r="D60"/>
+      <c r="C60" t="n">
+        <v>142</v>
+      </c>
+      <c r="D60" t="n">
+        <v>506</v>
+      </c>
       <c r="E60" t="n">
-        <v>389</v>
-      </c>
-      <c r="F60"/>
-      <c r="G60"/>
+        <v>123</v>
+      </c>
+      <c r="F60" t="n">
+        <v>625862</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3401976</v>
+      </c>
       <c r="H60" t="n">
-        <v>2710407</v>
+        <v>1016344</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61" t="n">
         <v>2023</v>
       </c>
-      <c r="C61"/>
-      <c r="D61"/>
+      <c r="C61" t="n">
+        <v>180</v>
+      </c>
+      <c r="D61" t="n">
+        <v>643</v>
+      </c>
       <c r="E61" t="n">
-        <v>185</v>
-      </c>
-      <c r="F61"/>
-      <c r="G61"/>
+        <v>133</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1014456</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4310757</v>
+      </c>
       <c r="H61" t="n">
-        <v>357420</v>
+        <v>1194970</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B62" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C62"/>
-      <c r="D62" t="n">
-        <v>10928</v>
-      </c>
-      <c r="E62" t="n">
-        <v>361</v>
-      </c>
-      <c r="F62"/>
-      <c r="G62" t="n">
-        <v>31898508</v>
-      </c>
-      <c r="H62" t="n">
-        <v>3602000</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62"/>
+      <c r="H62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B63" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C63"/>
-      <c r="D63" t="n">
-        <v>17492</v>
-      </c>
+        <v>2018</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4538</v>
+      </c>
+      <c r="D63"/>
       <c r="E63" t="n">
-        <v>508</v>
-      </c>
-      <c r="F63"/>
-      <c r="G63" t="n">
-        <v>60176445</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="F63" t="n">
+        <v>16239151</v>
+      </c>
+      <c r="G63"/>
       <c r="H63" t="n">
-        <v>4398619</v>
+        <v>2782000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B64" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C64"/>
-      <c r="D64" t="n">
-        <v>16292</v>
-      </c>
+        <v>2019</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4106</v>
+      </c>
+      <c r="D64"/>
       <c r="E64" t="n">
-        <v>456</v>
-      </c>
-      <c r="F64"/>
-      <c r="G64" t="n">
-        <v>56460458</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="F64" t="n">
+        <v>15481712</v>
+      </c>
+      <c r="G64"/>
       <c r="H64" t="n">
-        <v>3861715</v>
+        <v>2676520</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B65" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C65"/>
-      <c r="D65" t="n">
-        <v>18508</v>
-      </c>
+        <v>2020</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4080</v>
+      </c>
+      <c r="D65"/>
       <c r="E65" t="n">
-        <v>145</v>
-      </c>
-      <c r="F65"/>
-      <c r="G65" t="n">
-        <v>66269410</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="F65" t="n">
+        <v>14220957</v>
+      </c>
+      <c r="G65"/>
       <c r="H65" t="n">
-        <v>1078269</v>
+        <v>2617529</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B66" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C66"/>
-      <c r="D66" t="n">
-        <v>16896</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3822</v>
+      </c>
+      <c r="D66"/>
       <c r="E66" t="n">
-        <v>396</v>
-      </c>
-      <c r="F66"/>
-      <c r="G66" t="n">
-        <v>68219886</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12330081</v>
+      </c>
+      <c r="G66"/>
       <c r="H66" t="n">
-        <v>4244012</v>
+        <v>2991065</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B67" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C67"/>
-      <c r="D67" t="n">
-        <v>17952</v>
-      </c>
+        <v>2022</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4409</v>
+      </c>
+      <c r="D67"/>
       <c r="E67" t="n">
-        <v>73</v>
-      </c>
-      <c r="F67"/>
-      <c r="G67" t="n">
-        <v>83400088</v>
-      </c>
+        <v>389</v>
+      </c>
+      <c r="F67" t="n">
+        <v>15611511</v>
+      </c>
+      <c r="G67"/>
       <c r="H67" t="n">
-        <v>462380</v>
+        <v>2710407</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B68" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C68"/>
-      <c r="D68" t="n">
-        <v>2409</v>
-      </c>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68" t="n">
-        <v>11555958</v>
-      </c>
-      <c r="H68"/>
+        <v>2023</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4613</v>
+      </c>
+      <c r="D68"/>
+      <c r="E68" t="n">
+        <v>185</v>
+      </c>
+      <c r="F68" t="n">
+        <v>17355870</v>
+      </c>
+      <c r="G68"/>
+      <c r="H68" t="n">
+        <v>357420</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B69" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C69"/>
-      <c r="D69" t="n">
-        <v>2760</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69"/>
       <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69" t="n">
-        <v>11803595</v>
-      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69"/>
       <c r="H69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B70" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C70"/>
+        <v>2018</v>
+      </c>
+      <c r="C70" t="n">
+        <v>32235</v>
+      </c>
       <c r="D70" t="n">
-        <v>3230</v>
-      </c>
-      <c r="E70"/>
-      <c r="F70"/>
+        <v>10928</v>
+      </c>
+      <c r="E70" t="n">
+        <v>361</v>
+      </c>
+      <c r="F70" t="n">
+        <v>104038514</v>
+      </c>
       <c r="G70" t="n">
-        <v>13191162</v>
-      </c>
-      <c r="H70"/>
+        <v>31898508</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3602000</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B71" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C71"/>
+        <v>2019</v>
+      </c>
+      <c r="C71" t="n">
+        <v>32767</v>
+      </c>
       <c r="D71" t="n">
-        <v>2972</v>
-      </c>
-      <c r="E71"/>
-      <c r="F71"/>
+        <v>17492</v>
+      </c>
+      <c r="E71" t="n">
+        <v>508</v>
+      </c>
+      <c r="F71" t="n">
+        <v>112516454</v>
+      </c>
       <c r="G71" t="n">
-        <v>13921984</v>
-      </c>
-      <c r="H71"/>
+        <v>60176445</v>
+      </c>
+      <c r="H71" t="n">
+        <v>4398619</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B72" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C72"/>
+        <v>2020</v>
+      </c>
+      <c r="C72" t="n">
+        <v>31945</v>
+      </c>
       <c r="D72" t="n">
-        <v>3301</v>
-      </c>
-      <c r="E72"/>
-      <c r="F72"/>
+        <v>16292</v>
+      </c>
+      <c r="E72" t="n">
+        <v>456</v>
+      </c>
+      <c r="F72" t="n">
+        <v>105548078</v>
+      </c>
       <c r="G72" t="n">
-        <v>19474255</v>
-      </c>
-      <c r="H72"/>
+        <v>56460458</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3861715</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B73" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C73"/>
+        <v>2021</v>
+      </c>
+      <c r="C73" t="n">
+        <v>36407</v>
+      </c>
       <c r="D73" t="n">
-        <v>3547</v>
-      </c>
-      <c r="E73"/>
-      <c r="F73"/>
+        <v>18508</v>
+      </c>
+      <c r="E73" t="n">
+        <v>145</v>
+      </c>
+      <c r="F73" t="n">
+        <v>126191511</v>
+      </c>
       <c r="G73" t="n">
-        <v>22031108</v>
-      </c>
-      <c r="H73"/>
+        <v>66269410</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1078269</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B74" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C74"/>
+        <v>2022</v>
+      </c>
+      <c r="C74" t="n">
+        <v>33027</v>
+      </c>
       <c r="D74" t="n">
-        <v>38769</v>
+        <v>16896</v>
       </c>
       <c r="E74" t="n">
-        <v>3798</v>
-      </c>
-      <c r="F74"/>
+        <v>396</v>
+      </c>
+      <c r="F74" t="n">
+        <v>126963518</v>
+      </c>
       <c r="G74" t="n">
-        <v>151172219</v>
+        <v>68219886</v>
       </c>
       <c r="H74" t="n">
-        <v>13748000</v>
+        <v>4244012</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B75" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C75"/>
+        <v>2023</v>
+      </c>
+      <c r="C75" t="n">
+        <v>35180</v>
+      </c>
       <c r="D75" t="n">
-        <v>41194</v>
+        <v>17952</v>
       </c>
       <c r="E75" t="n">
-        <v>3655</v>
-      </c>
-      <c r="F75"/>
+        <v>73</v>
+      </c>
+      <c r="F75" t="n">
+        <v>158386225</v>
+      </c>
       <c r="G75" t="n">
-        <v>163739128</v>
+        <v>83400088</v>
       </c>
       <c r="H75" t="n">
-        <v>16006249</v>
+        <v>462380</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B76" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C76"/>
-      <c r="D76" t="n">
-        <v>41086</v>
-      </c>
-      <c r="E76" t="n">
-        <v>3340</v>
-      </c>
-      <c r="F76"/>
-      <c r="G76" t="n">
-        <v>163570915</v>
-      </c>
-      <c r="H76" t="n">
-        <v>14969932</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C76" t="n">
+        <v>17464</v>
+      </c>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76" t="n">
+        <v>83267361</v>
+      </c>
+      <c r="G76"/>
+      <c r="H76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B77" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C77"/>
+        <v>2018</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4530</v>
+      </c>
       <c r="D77" t="n">
-        <v>38459</v>
-      </c>
-      <c r="E77" t="n">
-        <v>3187</v>
-      </c>
-      <c r="F77"/>
+        <v>2409</v>
+      </c>
+      <c r="E77"/>
+      <c r="F77" t="n">
+        <v>21444102</v>
+      </c>
       <c r="G77" t="n">
-        <v>167315357</v>
-      </c>
-      <c r="H77" t="n">
-        <v>15421741</v>
-      </c>
+        <v>11555958</v>
+      </c>
+      <c r="H77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B78" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C78"/>
+        <v>2019</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4847</v>
+      </c>
       <c r="D78" t="n">
-        <v>37354</v>
-      </c>
-      <c r="E78" t="n">
-        <v>3446</v>
-      </c>
-      <c r="F78"/>
+        <v>2760</v>
+      </c>
+      <c r="E78"/>
+      <c r="F78" t="n">
+        <v>18102051</v>
+      </c>
       <c r="G78" t="n">
-        <v>129039089</v>
-      </c>
-      <c r="H78" t="n">
-        <v>16381183</v>
-      </c>
+        <v>11803595</v>
+      </c>
+      <c r="H78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B79" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C79"/>
+        <v>2020</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5811</v>
+      </c>
       <c r="D79" t="n">
-        <v>34380</v>
-      </c>
-      <c r="E79" t="n">
-        <v>5679</v>
-      </c>
-      <c r="F79"/>
+        <v>3230</v>
+      </c>
+      <c r="E79"/>
+      <c r="F79" t="n">
+        <v>20981338</v>
+      </c>
       <c r="G79" t="n">
-        <v>183804407</v>
-      </c>
-      <c r="H79" t="n">
-        <v>28573140</v>
-      </c>
+        <v>13191162</v>
+      </c>
+      <c r="H79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B80" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C80"/>
+        <v>2021</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5390</v>
+      </c>
       <c r="D80" t="n">
-        <v>9506</v>
+        <v>2972</v>
       </c>
       <c r="E80"/>
-      <c r="F80"/>
+      <c r="F80" t="n">
+        <v>23263240</v>
+      </c>
       <c r="G80" t="n">
-        <v>41723018</v>
+        <v>13921984</v>
       </c>
       <c r="H80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B81" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C81"/>
+        <v>2022</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5965</v>
+      </c>
       <c r="D81" t="n">
-        <v>9826</v>
+        <v>3301</v>
       </c>
       <c r="E81"/>
-      <c r="F81"/>
+      <c r="F81" t="n">
+        <v>32577049</v>
+      </c>
       <c r="G81" t="n">
-        <v>46930877</v>
+        <v>19474255</v>
       </c>
       <c r="H81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B82" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C82"/>
+        <v>2023</v>
+      </c>
+      <c r="C82" t="n">
+        <v>6336</v>
+      </c>
       <c r="D82" t="n">
-        <v>9148</v>
+        <v>3547</v>
       </c>
       <c r="E82"/>
-      <c r="F82"/>
+      <c r="F82" t="n">
+        <v>35761162</v>
+      </c>
       <c r="G82" t="n">
-        <v>46584211</v>
+        <v>22031108</v>
       </c>
       <c r="H82"/>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B83" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C83"/>
-      <c r="D83" t="n">
-        <v>9455</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C83" t="n">
+        <v>8271</v>
+      </c>
+      <c r="D83"/>
       <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83" t="n">
-        <v>51304167</v>
-      </c>
+      <c r="F83" t="n">
+        <v>43454593</v>
+      </c>
+      <c r="G83"/>
       <c r="H83"/>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B84" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C84"/>
+        <v>2018</v>
+      </c>
+      <c r="C84" t="n">
+        <v>76722</v>
+      </c>
       <c r="D84" t="n">
-        <v>8663</v>
-      </c>
-      <c r="E84"/>
-      <c r="F84"/>
+        <v>38769</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3798</v>
+      </c>
+      <c r="F84" t="n">
+        <v>283808045</v>
+      </c>
       <c r="G84" t="n">
-        <v>48028715</v>
-      </c>
-      <c r="H84"/>
+        <v>151172219</v>
+      </c>
+      <c r="H84" t="n">
+        <v>13748000</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B85" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C85"/>
+        <v>2019</v>
+      </c>
+      <c r="C85" t="n">
+        <v>78357</v>
+      </c>
       <c r="D85" t="n">
-        <v>8663</v>
-      </c>
-      <c r="E85"/>
-      <c r="F85"/>
+        <v>41194</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3655</v>
+      </c>
+      <c r="F85" t="n">
+        <v>297991831</v>
+      </c>
       <c r="G85" t="n">
-        <v>47106916</v>
-      </c>
-      <c r="H85"/>
+        <v>163739128</v>
+      </c>
+      <c r="H85" t="n">
+        <v>16006249</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B86" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C86"/>
+        <v>2020</v>
+      </c>
+      <c r="C86" t="n">
+        <v>81671</v>
+      </c>
       <c r="D86" t="n">
-        <v>2899</v>
+        <v>41086</v>
       </c>
       <c r="E86" t="n">
-        <v>2529</v>
-      </c>
-      <c r="F86"/>
+        <v>3340</v>
+      </c>
+      <c r="F86" t="n">
+        <v>311359416</v>
+      </c>
       <c r="G86" t="n">
-        <v>6753526</v>
+        <v>163570915</v>
       </c>
       <c r="H86" t="n">
-        <v>5378000</v>
+        <v>14969932</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B87" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C87"/>
+        <v>2021</v>
+      </c>
+      <c r="C87" t="n">
+        <v>75814</v>
+      </c>
       <c r="D87" t="n">
-        <v>3100</v>
+        <v>38459</v>
       </c>
       <c r="E87" t="n">
-        <v>2728</v>
-      </c>
-      <c r="F87"/>
+        <v>3187</v>
+      </c>
+      <c r="F87" t="n">
+        <v>314875528</v>
+      </c>
       <c r="G87" t="n">
-        <v>7099317</v>
+        <v>167315357</v>
       </c>
       <c r="H87" t="n">
-        <v>5727432</v>
+        <v>15421741</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B88" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C88"/>
+        <v>2022</v>
+      </c>
+      <c r="C88" t="n">
+        <v>71774</v>
+      </c>
       <c r="D88" t="n">
-        <v>2732</v>
+        <v>37354</v>
       </c>
       <c r="E88" t="n">
-        <v>2388</v>
-      </c>
-      <c r="F88"/>
+        <v>3446</v>
+      </c>
+      <c r="F88" t="n">
+        <v>319548036</v>
+      </c>
       <c r="G88" t="n">
-        <v>6028456</v>
+        <v>129039089</v>
       </c>
       <c r="H88" t="n">
-        <v>4677074</v>
+        <v>16381183</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B89" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C89"/>
+        <v>2023</v>
+      </c>
+      <c r="C89" t="n">
+        <v>67053</v>
+      </c>
       <c r="D89" t="n">
-        <v>4143</v>
+        <v>34380</v>
       </c>
       <c r="E89" t="n">
-        <v>3690</v>
-      </c>
-      <c r="F89"/>
+        <v>5679</v>
+      </c>
+      <c r="F89" t="n">
+        <v>341732354</v>
+      </c>
       <c r="G89" t="n">
-        <v>9204773</v>
+        <v>183804407</v>
       </c>
       <c r="H89" t="n">
-        <v>7547190</v>
+        <v>28573140</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B90" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C90"/>
-      <c r="D90" t="n">
-        <v>4117</v>
-      </c>
-      <c r="E90" t="n">
-        <v>3693</v>
-      </c>
-      <c r="F90"/>
-      <c r="G90" t="n">
-        <v>10606049</v>
-      </c>
-      <c r="H90" t="n">
-        <v>8769907</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C90" t="n">
+        <v>78486</v>
+      </c>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90" t="n">
+        <v>416966035</v>
+      </c>
+      <c r="G90"/>
+      <c r="H90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B91" t="n">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="C91"/>
       <c r="D91" t="n">
-        <v>3676</v>
-      </c>
-      <c r="E91" t="n">
-        <v>3238</v>
-      </c>
+        <v>9506</v>
+      </c>
+      <c r="E91"/>
       <c r="F91"/>
       <c r="G91" t="n">
-        <v>13475102</v>
-      </c>
-      <c r="H91" t="n">
-        <v>11394220</v>
-      </c>
+        <v>41723018</v>
+      </c>
+      <c r="H91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B92" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C92"/>
       <c r="D92" t="n">
-        <v>17852</v>
-      </c>
-      <c r="E92" t="n">
-        <v>17827</v>
-      </c>
+        <v>9826</v>
+      </c>
+      <c r="E92"/>
       <c r="F92"/>
       <c r="G92" t="n">
-        <v>38447654</v>
-      </c>
-      <c r="H92" t="n">
-        <v>38467000</v>
-      </c>
+        <v>46930877</v>
+      </c>
+      <c r="H92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B93" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C93"/>
       <c r="D93" t="n">
-        <v>17283</v>
-      </c>
-      <c r="E93" t="n">
-        <v>17239</v>
-      </c>
+        <v>9148</v>
+      </c>
+      <c r="E93"/>
       <c r="F93"/>
       <c r="G93" t="n">
-        <v>36041259</v>
-      </c>
-      <c r="H93" t="n">
-        <v>35674249</v>
-      </c>
+        <v>46584211</v>
+      </c>
+      <c r="H93"/>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B94" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C94"/>
       <c r="D94" t="n">
-        <v>18436</v>
-      </c>
-      <c r="E94" t="n">
-        <v>22115</v>
-      </c>
+        <v>9455</v>
+      </c>
+      <c r="E94"/>
       <c r="F94"/>
       <c r="G94" t="n">
-        <v>35610954</v>
-      </c>
-      <c r="H94" t="n">
-        <v>41005875</v>
-      </c>
+        <v>51304167</v>
+      </c>
+      <c r="H94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B95" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C95"/>
       <c r="D95" t="n">
-        <v>18025</v>
-      </c>
-      <c r="E95" t="n">
-        <v>17882</v>
-      </c>
+        <v>8663</v>
+      </c>
+      <c r="E95"/>
       <c r="F95"/>
       <c r="G95" t="n">
-        <v>38483582</v>
-      </c>
-      <c r="H95" t="n">
-        <v>38258905</v>
-      </c>
+        <v>48028715</v>
+      </c>
+      <c r="H95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B96" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C96"/>
       <c r="D96" t="n">
-        <v>18557</v>
-      </c>
-      <c r="E96" t="n">
-        <v>18646</v>
-      </c>
+        <v>8663</v>
+      </c>
+      <c r="E96"/>
       <c r="F96"/>
       <c r="G96" t="n">
-        <v>54304484</v>
-      </c>
-      <c r="H96" t="n">
-        <v>53006770</v>
-      </c>
+        <v>47106916</v>
+      </c>
+      <c r="H96"/>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B97" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C97"/>
+        <v>2018</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5798</v>
+      </c>
       <c r="D97" t="n">
-        <v>17785</v>
+        <v>2899</v>
       </c>
       <c r="E97" t="n">
-        <v>17773</v>
-      </c>
-      <c r="F97"/>
+        <v>2529</v>
+      </c>
+      <c r="F97" t="n">
+        <v>13482128</v>
+      </c>
       <c r="G97" t="n">
-        <v>61300859</v>
+        <v>6753526</v>
       </c>
       <c r="H97" t="n">
-        <v>58819110</v>
+        <v>5378000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B98" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C98"/>
+        <v>2019</v>
+      </c>
+      <c r="C98" t="n">
+        <v>6201</v>
+      </c>
       <c r="D98" t="n">
-        <v>557</v>
-      </c>
-      <c r="E98"/>
-      <c r="F98"/>
+        <v>3100</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2728</v>
+      </c>
+      <c r="F98" t="n">
+        <v>14195156</v>
+      </c>
       <c r="G98" t="n">
-        <v>1595329</v>
-      </c>
-      <c r="H98"/>
+        <v>7099317</v>
+      </c>
+      <c r="H98" t="n">
+        <v>5727432</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B99" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C99"/>
+        <v>2020</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5557</v>
+      </c>
       <c r="D99" t="n">
-        <v>608</v>
-      </c>
-      <c r="E99"/>
-      <c r="F99"/>
+        <v>2732</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2388</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12407013</v>
+      </c>
       <c r="G99" t="n">
-        <v>1677561</v>
-      </c>
-      <c r="H99"/>
+        <v>6028456</v>
+      </c>
+      <c r="H99" t="n">
+        <v>4677074</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B100" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C100"/>
+        <v>2021</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8281</v>
+      </c>
       <c r="D100" t="n">
-        <v>604</v>
-      </c>
-      <c r="E100"/>
-      <c r="F100"/>
+        <v>4143</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3690</v>
+      </c>
+      <c r="F100" t="n">
+        <v>18387733</v>
+      </c>
       <c r="G100" t="n">
-        <v>1887695</v>
-      </c>
-      <c r="H100"/>
+        <v>9204773</v>
+      </c>
+      <c r="H100" t="n">
+        <v>7547190</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B101" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C101"/>
+        <v>2022</v>
+      </c>
+      <c r="C101" t="n">
+        <v>8234</v>
+      </c>
       <c r="D101" t="n">
-        <v>537</v>
-      </c>
-      <c r="E101"/>
-      <c r="F101"/>
+        <v>4117</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3693</v>
+      </c>
+      <c r="F101" t="n">
+        <v>21216949</v>
+      </c>
       <c r="G101" t="n">
-        <v>1760330</v>
-      </c>
-      <c r="H101"/>
+        <v>10606049</v>
+      </c>
+      <c r="H101" t="n">
+        <v>8769907</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B102" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C102"/>
+        <v>2023</v>
+      </c>
+      <c r="C102" t="n">
+        <v>7353</v>
+      </c>
       <c r="D102" t="n">
-        <v>398</v>
-      </c>
-      <c r="E102"/>
-      <c r="F102"/>
+        <v>3676</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3238</v>
+      </c>
+      <c r="F102" t="n">
+        <v>26987699</v>
+      </c>
       <c r="G102" t="n">
-        <v>1234288</v>
-      </c>
-      <c r="H102"/>
+        <v>13475102</v>
+      </c>
+      <c r="H102" t="n">
+        <v>11394220</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B103" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C103"/>
-      <c r="D103" t="n">
-        <v>488</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C103" t="n">
+        <v>8863</v>
+      </c>
+      <c r="D103"/>
       <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103" t="n">
-        <v>1514624</v>
-      </c>
+      <c r="F103" t="n">
+        <v>28954965</v>
+      </c>
+      <c r="G103"/>
       <c r="H103"/>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B104" t="n">
         <v>2018</v>
       </c>
-      <c r="C104"/>
+      <c r="C104" t="n">
+        <v>35801</v>
+      </c>
       <c r="D104" t="n">
-        <v>295</v>
-      </c>
-      <c r="E104"/>
-      <c r="F104"/>
+        <v>17852</v>
+      </c>
+      <c r="E104" t="n">
+        <v>17827</v>
+      </c>
+      <c r="F104" t="n">
+        <v>77509990</v>
+      </c>
       <c r="G104" t="n">
-        <v>1325848</v>
-      </c>
-      <c r="H104"/>
+        <v>38447654</v>
+      </c>
+      <c r="H104" t="n">
+        <v>38467000</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B105" t="n">
         <v>2019</v>
       </c>
-      <c r="C105"/>
+      <c r="C105" t="n">
+        <v>34630</v>
+      </c>
       <c r="D105" t="n">
-        <v>299</v>
-      </c>
-      <c r="E105"/>
-      <c r="F105"/>
+        <v>17283</v>
+      </c>
+      <c r="E105" t="n">
+        <v>17239</v>
+      </c>
+      <c r="F105" t="n">
+        <v>71970677</v>
+      </c>
       <c r="G105" t="n">
-        <v>1230429</v>
-      </c>
-      <c r="H105"/>
+        <v>36041259</v>
+      </c>
+      <c r="H105" t="n">
+        <v>35674249</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B106" t="n">
         <v>2020</v>
       </c>
-      <c r="C106"/>
+      <c r="C106" t="n">
+        <v>36770</v>
+      </c>
       <c r="D106" t="n">
-        <v>490</v>
-      </c>
-      <c r="E106"/>
-      <c r="F106"/>
+        <v>18436</v>
+      </c>
+      <c r="E106" t="n">
+        <v>22115</v>
+      </c>
+      <c r="F106" t="n">
+        <v>69683775</v>
+      </c>
       <c r="G106" t="n">
-        <v>1507304</v>
-      </c>
-      <c r="H106"/>
+        <v>35610954</v>
+      </c>
+      <c r="H106" t="n">
+        <v>41005875</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B107" t="n">
         <v>2021</v>
       </c>
-      <c r="C107"/>
+      <c r="C107" t="n">
+        <v>35911</v>
+      </c>
       <c r="D107" t="n">
-        <v>951</v>
-      </c>
-      <c r="E107"/>
-      <c r="F107"/>
+        <v>18025</v>
+      </c>
+      <c r="E107" t="n">
+        <v>17882</v>
+      </c>
+      <c r="F107" t="n">
+        <v>77541214</v>
+      </c>
       <c r="G107" t="n">
-        <v>4005671</v>
-      </c>
-      <c r="H107"/>
+        <v>38483582</v>
+      </c>
+      <c r="H107" t="n">
+        <v>38258905</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B108" t="n">
         <v>2022</v>
       </c>
-      <c r="C108"/>
+      <c r="C108" t="n">
+        <v>37414</v>
+      </c>
       <c r="D108" t="n">
-        <v>1131</v>
-      </c>
-      <c r="E108"/>
-      <c r="F108"/>
+        <v>18557</v>
+      </c>
+      <c r="E108" t="n">
+        <v>18646</v>
+      </c>
+      <c r="F108" t="n">
+        <v>106604291</v>
+      </c>
       <c r="G108" t="n">
-        <v>5027553</v>
-      </c>
-      <c r="H108"/>
+        <v>54304484</v>
+      </c>
+      <c r="H108" t="n">
+        <v>53006770</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B109" t="n">
         <v>2023</v>
       </c>
-      <c r="C109"/>
+      <c r="C109" t="n">
+        <v>35697</v>
+      </c>
       <c r="D109" t="n">
-        <v>441</v>
-      </c>
-      <c r="E109"/>
-      <c r="F109"/>
+        <v>17785</v>
+      </c>
+      <c r="E109" t="n">
+        <v>17773</v>
+      </c>
+      <c r="F109" t="n">
+        <v>118746186</v>
+      </c>
       <c r="G109" t="n">
-        <v>1872838</v>
-      </c>
-      <c r="H109"/>
+        <v>61300859</v>
+      </c>
+      <c r="H109" t="n">
+        <v>58819110</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B110" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C110"/>
-      <c r="D110" t="n">
-        <v>36728</v>
-      </c>
-      <c r="E110" t="n">
-        <v>2477</v>
-      </c>
-      <c r="F110"/>
-      <c r="G110" t="n">
-        <v>127299648</v>
-      </c>
-      <c r="H110" t="n">
-        <v>19662000</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C110" t="n">
+        <v>38971</v>
+      </c>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110" t="n">
+        <v>119248561</v>
+      </c>
+      <c r="G110"/>
+      <c r="H110"/>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B111" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C111"/>
       <c r="D111" t="n">
-        <v>41501</v>
-      </c>
-      <c r="E111" t="n">
-        <v>2472</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="E111"/>
       <c r="F111"/>
       <c r="G111" t="n">
-        <v>142556068</v>
-      </c>
-      <c r="H111" t="n">
-        <v>16950529</v>
-      </c>
+        <v>1595329</v>
+      </c>
+      <c r="H111"/>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B112" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C112"/>
+        <v>2019</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1216</v>
+      </c>
       <c r="D112" t="n">
-        <v>36518</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1891</v>
-      </c>
-      <c r="F112"/>
+        <v>608</v>
+      </c>
+      <c r="E112"/>
+      <c r="F112" t="n">
+        <v>3351296</v>
+      </c>
       <c r="G112" t="n">
-        <v>119070198</v>
-      </c>
-      <c r="H112" t="n">
-        <v>11600943</v>
-      </c>
+        <v>1677561</v>
+      </c>
+      <c r="H112"/>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B113" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C113"/>
+        <v>2020</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1208</v>
+      </c>
       <c r="D113" t="n">
-        <v>44285</v>
-      </c>
-      <c r="E113" t="n">
-        <v>2285</v>
-      </c>
-      <c r="F113"/>
+        <v>604</v>
+      </c>
+      <c r="E113"/>
+      <c r="F113" t="n">
+        <v>3765336</v>
+      </c>
       <c r="G113" t="n">
-        <v>159056227</v>
-      </c>
-      <c r="H113" t="n">
-        <v>15140190</v>
-      </c>
+        <v>1887695</v>
+      </c>
+      <c r="H113"/>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B114" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C114"/>
+        <v>2021</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1074</v>
+      </c>
       <c r="D114" t="n">
-        <v>32639</v>
-      </c>
-      <c r="E114" t="n">
-        <v>2450</v>
-      </c>
-      <c r="F114"/>
+        <v>537</v>
+      </c>
+      <c r="E114"/>
+      <c r="F114" t="n">
+        <v>3523794</v>
+      </c>
       <c r="G114" t="n">
-        <v>117439451</v>
-      </c>
-      <c r="H114" t="n">
-        <v>18529700</v>
-      </c>
+        <v>1760330</v>
+      </c>
+      <c r="H114"/>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B115" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C115"/>
+        <v>2022</v>
+      </c>
+      <c r="C115" t="n">
+        <v>796</v>
+      </c>
       <c r="D115" t="n">
-        <v>37579</v>
-      </c>
-      <c r="E115" t="n">
-        <v>1973</v>
-      </c>
-      <c r="F115"/>
+        <v>398</v>
+      </c>
+      <c r="E115"/>
+      <c r="F115" t="n">
+        <v>814308</v>
+      </c>
       <c r="G115" t="n">
-        <v>173521362</v>
-      </c>
-      <c r="H115" t="n">
-        <v>15898980</v>
-      </c>
+        <v>1234288</v>
+      </c>
+      <c r="H115"/>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B116" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C116"/>
+        <v>2023</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
       <c r="D116" t="n">
-        <v>3744</v>
-      </c>
-      <c r="E116" t="n">
-        <v>3339</v>
-      </c>
-      <c r="F116"/>
+        <v>488</v>
+      </c>
+      <c r="E116"/>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
       <c r="G116" t="n">
-        <v>11878218</v>
-      </c>
-      <c r="H116" t="n">
-        <v>10765000</v>
-      </c>
+        <v>1514624</v>
+      </c>
+      <c r="H116"/>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B117" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C117"/>
-      <c r="D117" t="n">
-        <v>4215</v>
-      </c>
-      <c r="E117" t="n">
-        <v>3599</v>
-      </c>
-      <c r="F117"/>
-      <c r="G117" t="n">
-        <v>12475637</v>
-      </c>
-      <c r="H117" t="n">
-        <v>11338369</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117" t="n">
+        <v>2997000</v>
+      </c>
+      <c r="G117"/>
+      <c r="H117"/>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B118" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C118"/>
       <c r="D118" t="n">
-        <v>4477</v>
-      </c>
-      <c r="E118" t="n">
-        <v>3848</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="E118"/>
       <c r="F118"/>
       <c r="G118" t="n">
-        <v>12876898</v>
-      </c>
-      <c r="H118" t="n">
-        <v>11510127</v>
-      </c>
+        <v>1325848</v>
+      </c>
+      <c r="H118"/>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B119" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C119"/>
       <c r="D119" t="n">
-        <v>5135</v>
-      </c>
-      <c r="E119" t="n">
-        <v>4686</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="E119"/>
       <c r="F119"/>
       <c r="G119" t="n">
-        <v>15110911</v>
-      </c>
-      <c r="H119" t="n">
-        <v>14598743</v>
-      </c>
+        <v>1230429</v>
+      </c>
+      <c r="H119"/>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B120" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C120"/>
+        <v>2020</v>
+      </c>
+      <c r="C120" t="n">
+        <v>10566</v>
+      </c>
       <c r="D120" t="n">
-        <v>4859</v>
-      </c>
-      <c r="E120" t="n">
-        <v>4229</v>
-      </c>
-      <c r="F120"/>
+        <v>490</v>
+      </c>
+      <c r="E120"/>
+      <c r="F120" t="n">
+        <v>73701047</v>
+      </c>
       <c r="G120" t="n">
-        <v>19715333</v>
-      </c>
-      <c r="H120" t="n">
-        <v>17645056</v>
-      </c>
+        <v>1507304</v>
+      </c>
+      <c r="H120"/>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B121" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C121"/>
+        <v>2021</v>
+      </c>
+      <c r="C121" t="n">
+        <v>11454</v>
+      </c>
       <c r="D121" t="n">
-        <v>4258</v>
-      </c>
-      <c r="E121" t="n">
-        <v>3513</v>
-      </c>
-      <c r="F121"/>
+        <v>951</v>
+      </c>
+      <c r="E121"/>
+      <c r="F121" t="n">
+        <v>70714870</v>
+      </c>
       <c r="G121" t="n">
-        <v>18073212</v>
-      </c>
-      <c r="H121" t="n">
-        <v>15539120</v>
-      </c>
+        <v>4005671</v>
+      </c>
+      <c r="H121"/>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B122" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C122"/>
+        <v>2022</v>
+      </c>
+      <c r="C122" t="n">
+        <v>10566</v>
+      </c>
       <c r="D122" t="n">
-        <v>830</v>
-      </c>
-      <c r="E122" t="n">
-        <v>849</v>
-      </c>
-      <c r="F122"/>
+        <v>1131</v>
+      </c>
+      <c r="E122"/>
+      <c r="F122" t="n">
+        <v>80100147</v>
+      </c>
       <c r="G122" t="n">
-        <v>1998757</v>
-      </c>
-      <c r="H122" t="n">
-        <v>1874000</v>
-      </c>
+        <v>5027553</v>
+      </c>
+      <c r="H122"/>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B123" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C123"/>
+        <v>2023</v>
+      </c>
+      <c r="C123" t="n">
+        <v>11276</v>
+      </c>
       <c r="D123" t="n">
-        <v>609</v>
-      </c>
-      <c r="E123" t="n">
-        <v>578</v>
-      </c>
-      <c r="F123"/>
+        <v>441</v>
+      </c>
+      <c r="E123"/>
+      <c r="F123" t="n">
+        <v>85567847</v>
+      </c>
       <c r="G123" t="n">
-        <v>1657737</v>
-      </c>
-      <c r="H123" t="n">
-        <v>1622373</v>
-      </c>
+        <v>1872838</v>
+      </c>
+      <c r="H123"/>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B124" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C124"/>
-      <c r="D124" t="n">
-        <v>717</v>
-      </c>
-      <c r="E124" t="n">
-        <v>642</v>
-      </c>
-      <c r="F124"/>
-      <c r="G124" t="n">
-        <v>2201288</v>
-      </c>
-      <c r="H124" t="n">
-        <v>1781836</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C124" t="n">
+        <v>10672</v>
+      </c>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124" t="n">
+        <v>119706431</v>
+      </c>
+      <c r="G124"/>
+      <c r="H124"/>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B125" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C125"/>
+        <v>2018</v>
+      </c>
+      <c r="C125" t="n">
+        <v>73473</v>
+      </c>
       <c r="D125" t="n">
-        <v>901</v>
+        <v>36728</v>
       </c>
       <c r="E125" t="n">
-        <v>719</v>
-      </c>
-      <c r="F125"/>
+        <v>2477</v>
+      </c>
+      <c r="F125" t="n">
+        <v>240404264</v>
+      </c>
       <c r="G125" t="n">
-        <v>3162543</v>
+        <v>127299648</v>
       </c>
       <c r="H125" t="n">
-        <v>2051767</v>
+        <v>19662000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B126" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C126"/>
+        <v>2019</v>
+      </c>
+      <c r="C126" t="n">
+        <v>82750</v>
+      </c>
       <c r="D126" t="n">
-        <v>870</v>
+        <v>41501</v>
       </c>
       <c r="E126" t="n">
-        <v>755</v>
-      </c>
-      <c r="F126"/>
+        <v>2472</v>
+      </c>
+      <c r="F126" t="n">
+        <v>276181292</v>
+      </c>
       <c r="G126" t="n">
-        <v>3305535</v>
+        <v>142556068</v>
       </c>
       <c r="H126" t="n">
-        <v>2438935</v>
+        <v>16950529</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B127" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C127"/>
+        <v>2020</v>
+      </c>
+      <c r="C127" t="n">
+        <v>72966</v>
+      </c>
       <c r="D127" t="n">
-        <v>784</v>
+        <v>36518</v>
       </c>
       <c r="E127" t="n">
-        <v>173</v>
-      </c>
-      <c r="F127"/>
+        <v>1891</v>
+      </c>
+      <c r="F127" t="n">
+        <v>234944751</v>
+      </c>
       <c r="G127" t="n">
-        <v>3009566</v>
+        <v>119070198</v>
       </c>
       <c r="H127" t="n">
-        <v>1038900</v>
+        <v>11600943</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B128" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C128"/>
+        <v>2021</v>
+      </c>
+      <c r="C128" t="n">
+        <v>88609</v>
+      </c>
       <c r="D128" t="n">
-        <v>5015</v>
+        <v>44285</v>
       </c>
       <c r="E128" t="n">
-        <v>4620</v>
-      </c>
-      <c r="F128"/>
+        <v>2285</v>
+      </c>
+      <c r="F128" t="n">
+        <v>316399212</v>
+      </c>
       <c r="G128" t="n">
-        <v>32393084</v>
+        <v>159056227</v>
       </c>
       <c r="H128" t="n">
-        <v>26527000</v>
+        <v>15140190</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B129" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C129"/>
+        <v>2022</v>
+      </c>
+      <c r="C129" t="n">
+        <v>64708</v>
+      </c>
       <c r="D129" t="n">
-        <v>5310</v>
+        <v>32639</v>
       </c>
       <c r="E129" t="n">
-        <v>5220</v>
-      </c>
-      <c r="F129"/>
+        <v>2450</v>
+      </c>
+      <c r="F129" t="n">
+        <v>237530780</v>
+      </c>
       <c r="G129" t="n">
-        <v>29441292</v>
+        <v>117439451</v>
       </c>
       <c r="H129" t="n">
-        <v>27519909</v>
+        <v>18529700</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B130" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C130"/>
+        <v>2023</v>
+      </c>
+      <c r="C130" t="n">
+        <v>74664</v>
+      </c>
       <c r="D130" t="n">
-        <v>4860</v>
+        <v>37579</v>
       </c>
       <c r="E130" t="n">
-        <v>4805</v>
-      </c>
-      <c r="F130"/>
+        <v>1973</v>
+      </c>
+      <c r="F130" t="n">
+        <v>451132063</v>
+      </c>
       <c r="G130" t="n">
-        <v>27296889</v>
+        <v>173521362</v>
       </c>
       <c r="H130" t="n">
-        <v>26467883</v>
+        <v>15898980</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B131" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C131"/>
-      <c r="D131" t="n">
-        <v>4820</v>
-      </c>
-      <c r="E131" t="n">
-        <v>4400</v>
-      </c>
-      <c r="F131"/>
-      <c r="G131" t="n">
-        <v>26569863</v>
-      </c>
-      <c r="H131" t="n">
-        <v>23425000</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C131" t="n">
+        <v>66851</v>
+      </c>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131" t="n">
+        <v>269094696</v>
+      </c>
+      <c r="G131"/>
+      <c r="H131"/>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B132" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C132"/>
+        <v>2018</v>
+      </c>
+      <c r="C132" t="n">
+        <v>6900</v>
+      </c>
       <c r="D132" t="n">
-        <v>4670</v>
+        <v>3744</v>
       </c>
       <c r="E132" t="n">
-        <v>4400</v>
-      </c>
-      <c r="F132"/>
+        <v>3339</v>
+      </c>
+      <c r="F132" t="n">
+        <v>22473699</v>
+      </c>
       <c r="G132" t="n">
-        <v>25608541</v>
+        <v>11878218</v>
       </c>
       <c r="H132" t="n">
-        <v>29900800</v>
+        <v>10765000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B133" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C133"/>
+        <v>2019</v>
+      </c>
+      <c r="C133" t="n">
+        <v>7550</v>
+      </c>
       <c r="D133" t="n">
-        <v>4770</v>
+        <v>4215</v>
       </c>
       <c r="E133" t="n">
-        <v>2650</v>
-      </c>
-      <c r="F133"/>
+        <v>3599</v>
+      </c>
+      <c r="F133" t="n">
+        <v>23950442</v>
+      </c>
       <c r="G133" t="n">
-        <v>33820370</v>
+        <v>12475637</v>
       </c>
       <c r="H133" t="n">
-        <v>6651310</v>
+        <v>11338369</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B134" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C134"/>
+        <v>2020</v>
+      </c>
+      <c r="C134" t="n">
+        <v>8139</v>
+      </c>
       <c r="D134" t="n">
-        <v>417</v>
-      </c>
-      <c r="E134"/>
-      <c r="F134"/>
+        <v>4477</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3848</v>
+      </c>
+      <c r="F134" t="n">
+        <v>25010940</v>
+      </c>
       <c r="G134" t="n">
-        <v>3136002</v>
-      </c>
-      <c r="H134"/>
+        <v>12876898</v>
+      </c>
+      <c r="H134" t="n">
+        <v>11510127</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B135" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C135"/>
+        <v>2021</v>
+      </c>
+      <c r="C135" t="n">
+        <v>9629</v>
+      </c>
       <c r="D135" t="n">
-        <v>718</v>
-      </c>
-      <c r="E135"/>
-      <c r="F135"/>
+        <v>5135</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4686</v>
+      </c>
+      <c r="F135" t="n">
+        <v>30454465</v>
+      </c>
       <c r="G135" t="n">
-        <v>4384167</v>
-      </c>
-      <c r="H135"/>
+        <v>15110911</v>
+      </c>
+      <c r="H135" t="n">
+        <v>14598743</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B136" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C136"/>
+        <v>2022</v>
+      </c>
+      <c r="C136" t="n">
+        <v>8901</v>
+      </c>
       <c r="D136" t="n">
-        <v>634</v>
-      </c>
-      <c r="E136"/>
-      <c r="F136"/>
+        <v>4859</v>
+      </c>
+      <c r="E136" t="n">
+        <v>4229</v>
+      </c>
+      <c r="F136" t="n">
+        <v>37199170</v>
+      </c>
       <c r="G136" t="n">
-        <v>3844152</v>
-      </c>
-      <c r="H136"/>
+        <v>19715333</v>
+      </c>
+      <c r="H136" t="n">
+        <v>17645056</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B137" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C137"/>
+        <v>2023</v>
+      </c>
+      <c r="C137" t="n">
+        <v>7456</v>
+      </c>
       <c r="D137" t="n">
-        <v>903</v>
-      </c>
-      <c r="E137"/>
-      <c r="F137"/>
+        <v>4258</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3513</v>
+      </c>
+      <c r="F137" t="n">
+        <v>33285346</v>
+      </c>
       <c r="G137" t="n">
-        <v>5026735</v>
-      </c>
-      <c r="H137"/>
+        <v>18073212</v>
+      </c>
+      <c r="H137" t="n">
+        <v>15539120</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B138" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C138"/>
-      <c r="D138" t="n">
-        <v>1031</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C138" t="n">
+        <v>8111</v>
+      </c>
+      <c r="D138"/>
       <c r="E138"/>
-      <c r="F138"/>
-      <c r="G138" t="n">
-        <v>6232096</v>
-      </c>
+      <c r="F138" t="n">
+        <v>32522846</v>
+      </c>
+      <c r="G138"/>
       <c r="H138"/>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B139" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C139"/>
+        <v>2018</v>
+      </c>
+      <c r="C139" t="n">
+        <v>670</v>
+      </c>
       <c r="D139" t="n">
-        <v>1433</v>
-      </c>
-      <c r="E139"/>
-      <c r="F139"/>
+        <v>830</v>
+      </c>
+      <c r="E139" t="n">
+        <v>849</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1536947</v>
+      </c>
       <c r="G139" t="n">
-        <v>8017071</v>
-      </c>
-      <c r="H139"/>
+        <v>1998757</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1874000</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B140" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C140"/>
+        <v>2019</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1253</v>
+      </c>
       <c r="D140" t="n">
-        <v>36806</v>
+        <v>609</v>
       </c>
       <c r="E140" t="n">
-        <v>19354</v>
-      </c>
-      <c r="F140"/>
+        <v>578</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3693578</v>
+      </c>
       <c r="G140" t="n">
-        <v>104818808</v>
+        <v>1657737</v>
       </c>
       <c r="H140" t="n">
-        <v>50747000</v>
+        <v>1622373</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B141" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C141"/>
+        <v>2020</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1455</v>
+      </c>
       <c r="D141" t="n">
-        <v>39731</v>
+        <v>717</v>
       </c>
       <c r="E141" t="n">
-        <v>24268</v>
-      </c>
-      <c r="F141"/>
+        <v>642</v>
+      </c>
+      <c r="F141" t="n">
+        <v>4503655</v>
+      </c>
       <c r="G141" t="n">
-        <v>104159149</v>
+        <v>2201288</v>
       </c>
       <c r="H141" t="n">
-        <v>57171451</v>
+        <v>1781836</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B142" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C142"/>
+        <v>2021</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1804</v>
+      </c>
       <c r="D142" t="n">
-        <v>45418</v>
+        <v>901</v>
       </c>
       <c r="E142" t="n">
-        <v>23936</v>
-      </c>
-      <c r="F142"/>
+        <v>719</v>
+      </c>
+      <c r="F142" t="n">
+        <v>6328687</v>
+      </c>
       <c r="G142" t="n">
-        <v>121240880</v>
+        <v>3162543</v>
       </c>
       <c r="H142" t="n">
-        <v>54554807</v>
+        <v>2051767</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B143" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C143"/>
+        <v>2022</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1740</v>
+      </c>
       <c r="D143" t="n">
-        <v>39610</v>
+        <v>870</v>
       </c>
       <c r="E143" t="n">
-        <v>24288</v>
-      </c>
-      <c r="F143"/>
+        <v>755</v>
+      </c>
+      <c r="F143" t="n">
+        <v>6606725</v>
+      </c>
       <c r="G143" t="n">
-        <v>123529412</v>
+        <v>3305535</v>
       </c>
       <c r="H143" t="n">
-        <v>77883456</v>
+        <v>2438935</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B144" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C144"/>
+        <v>2023</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
       <c r="D144" t="n">
-        <v>42201</v>
+        <v>784</v>
       </c>
       <c r="E144" t="n">
-        <v>19834</v>
-      </c>
-      <c r="F144"/>
+        <v>173</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
       <c r="G144" t="n">
-        <v>185902438</v>
+        <v>3009566</v>
       </c>
       <c r="H144" t="n">
-        <v>90333025</v>
+        <v>1038900</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B145" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C145"/>
-      <c r="D145" t="n">
-        <v>40667</v>
-      </c>
-      <c r="E145" t="n">
-        <v>21178</v>
-      </c>
-      <c r="F145"/>
-      <c r="G145" t="n">
-        <v>185724551</v>
-      </c>
-      <c r="H145" t="n">
-        <v>101582700</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145"/>
+      <c r="H145"/>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B146" t="n">
         <v>2018</v>
       </c>
-      <c r="C146"/>
+      <c r="C146" t="n">
+        <v>9822</v>
+      </c>
       <c r="D146" t="n">
-        <v>697</v>
+        <v>5015</v>
       </c>
       <c r="E146" t="n">
-        <v>12</v>
-      </c>
-      <c r="F146"/>
+        <v>4620</v>
+      </c>
+      <c r="F146" t="n">
+        <v>59374000</v>
+      </c>
       <c r="G146" t="n">
-        <v>2331632</v>
+        <v>32393084</v>
       </c>
       <c r="H146" t="n">
-        <v>121000</v>
+        <v>26527000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B147" t="n">
         <v>2019</v>
       </c>
-      <c r="C147"/>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
       <c r="D147" t="n">
-        <v>665</v>
+        <v>5310</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147"/>
+        <v>5220</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
       <c r="G147" t="n">
-        <v>2003450</v>
+        <v>29441292</v>
       </c>
       <c r="H147" t="n">
-        <v>8870</v>
+        <v>27519909</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B148" t="n">
         <v>2020</v>
       </c>
-      <c r="C148"/>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
       <c r="D148" t="n">
-        <v>914</v>
+        <v>4860</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148"/>
+        <v>4805</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
       <c r="G148" t="n">
-        <v>2685738</v>
+        <v>27296889</v>
       </c>
       <c r="H148" t="n">
-        <v>1102</v>
+        <v>26467883</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B149" t="n">
         <v>2021</v>
       </c>
-      <c r="C149"/>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
       <c r="D149" t="n">
-        <v>867</v>
+        <v>4820</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
-      </c>
-      <c r="F149"/>
+        <v>4400</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
       <c r="G149" t="n">
-        <v>4984835</v>
+        <v>26569863</v>
       </c>
       <c r="H149" t="n">
-        <v>838</v>
+        <v>23425000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B150" t="n">
         <v>2022</v>
       </c>
-      <c r="C150"/>
+      <c r="C150" t="n">
+        <v>0</v>
+      </c>
       <c r="D150" t="n">
-        <v>423</v>
+        <v>4670</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150"/>
+        <v>4400</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
       <c r="G150" t="n">
-        <v>1398995</v>
+        <v>25608541</v>
       </c>
       <c r="H150" t="n">
-        <v>9418</v>
+        <v>29900800</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B151" t="n">
         <v>2023</v>
       </c>
-      <c r="C151"/>
+      <c r="C151" t="n">
+        <v>0</v>
+      </c>
       <c r="D151" t="n">
-        <v>317</v>
+        <v>4770</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151"/>
+        <v>2650</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
       <c r="G151" t="n">
-        <v>1184749</v>
+        <v>33820370</v>
       </c>
       <c r="H151" t="n">
-        <v>10000</v>
+        <v>6651310</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B152" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C152"/>
-      <c r="D152" t="n">
-        <v>12298</v>
-      </c>
-      <c r="E152" t="n">
-        <v>9826</v>
-      </c>
-      <c r="F152"/>
-      <c r="G152" t="n">
-        <v>30648544</v>
-      </c>
-      <c r="H152" t="n">
-        <v>24954000</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0</v>
+      </c>
+      <c r="D152"/>
+      <c r="E152"/>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152"/>
+      <c r="H152"/>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B153" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C153"/>
+        <v>2018</v>
+      </c>
+      <c r="C153" t="n">
+        <v>834</v>
+      </c>
       <c r="D153" t="n">
-        <v>12848</v>
-      </c>
-      <c r="E153" t="n">
-        <v>10091</v>
-      </c>
-      <c r="F153"/>
+        <v>417</v>
+      </c>
+      <c r="E153"/>
+      <c r="F153" t="n">
+        <v>6267162</v>
+      </c>
       <c r="G153" t="n">
-        <v>31861870</v>
-      </c>
-      <c r="H153" t="n">
-        <v>27861042</v>
-      </c>
+        <v>3136002</v>
+      </c>
+      <c r="H153"/>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B154" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C154"/>
+        <v>2019</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1436</v>
+      </c>
       <c r="D154" t="n">
-        <v>12371</v>
-      </c>
-      <c r="E154" t="n">
-        <v>9442</v>
-      </c>
-      <c r="F154"/>
+        <v>718</v>
+      </c>
+      <c r="E154"/>
+      <c r="F154" t="n">
+        <v>8771236</v>
+      </c>
       <c r="G154" t="n">
-        <v>39335532</v>
-      </c>
-      <c r="H154" t="n">
-        <v>27893432</v>
-      </c>
+        <v>4384167</v>
+      </c>
+      <c r="H154"/>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B155" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C155"/>
+        <v>2020</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1268</v>
+      </c>
       <c r="D155" t="n">
-        <v>11714</v>
-      </c>
-      <c r="E155" t="n">
-        <v>8967</v>
-      </c>
-      <c r="F155"/>
+        <v>634</v>
+      </c>
+      <c r="E155"/>
+      <c r="F155" t="n">
+        <v>7698047</v>
+      </c>
       <c r="G155" t="n">
-        <v>36587679</v>
-      </c>
-      <c r="H155" t="n">
-        <v>24696739</v>
-      </c>
+        <v>3844152</v>
+      </c>
+      <c r="H155"/>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B156" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C156"/>
+        <v>2021</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1807</v>
+      </c>
       <c r="D156" t="n">
-        <v>11211</v>
-      </c>
-      <c r="E156" t="n">
-        <v>8105</v>
-      </c>
-      <c r="F156"/>
+        <v>903</v>
+      </c>
+      <c r="E156"/>
+      <c r="F156" t="n">
+        <v>10055448</v>
+      </c>
       <c r="G156" t="n">
-        <v>36065959</v>
-      </c>
-      <c r="H156" t="n">
-        <v>24820229</v>
-      </c>
+        <v>5026735</v>
+      </c>
+      <c r="H156"/>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B157" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C157"/>
+        <v>2022</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2062</v>
+      </c>
       <c r="D157" t="n">
-        <v>11264</v>
-      </c>
-      <c r="E157" t="n">
-        <v>7735</v>
-      </c>
-      <c r="F157"/>
+        <v>1031</v>
+      </c>
+      <c r="E157"/>
+      <c r="F157" t="n">
+        <v>12486178</v>
+      </c>
       <c r="G157" t="n">
-        <v>37456631</v>
-      </c>
-      <c r="H157" t="n">
-        <v>26587640</v>
-      </c>
+        <v>6232096</v>
+      </c>
+      <c r="H157"/>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B158" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C158"/>
+        <v>2023</v>
+      </c>
+      <c r="C158" t="n">
+        <v>2865</v>
+      </c>
       <c r="D158" t="n">
-        <v>8239</v>
-      </c>
-      <c r="E158" t="n">
-        <v>99</v>
-      </c>
-      <c r="F158"/>
+        <v>1433</v>
+      </c>
+      <c r="E158"/>
+      <c r="F158" t="n">
+        <v>16044498</v>
+      </c>
       <c r="G158" t="n">
-        <v>36117260</v>
-      </c>
-      <c r="H158" t="n">
-        <v>676000</v>
-      </c>
+        <v>8017071</v>
+      </c>
+      <c r="H158"/>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B159" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C159"/>
-      <c r="D159" t="n">
-        <v>8084</v>
-      </c>
-      <c r="E159" t="n">
-        <v>163</v>
-      </c>
-      <c r="F159"/>
-      <c r="G159" t="n">
-        <v>28264134</v>
-      </c>
-      <c r="H159" t="n">
-        <v>920679</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C159" t="n">
+        <v>2349</v>
+      </c>
+      <c r="D159"/>
+      <c r="E159"/>
+      <c r="F159" t="n">
+        <v>13826133</v>
+      </c>
+      <c r="G159"/>
+      <c r="H159"/>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B160" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C160"/>
+        <v>2018</v>
+      </c>
+      <c r="C160" t="n">
+        <v>73613</v>
+      </c>
       <c r="D160" t="n">
-        <v>8690</v>
+        <v>36806</v>
       </c>
       <c r="E160" t="n">
-        <v>93</v>
-      </c>
-      <c r="F160"/>
+        <v>19354</v>
+      </c>
+      <c r="F160" t="n">
+        <v>209334202</v>
+      </c>
       <c r="G160" t="n">
-        <v>29684045</v>
+        <v>104818808</v>
       </c>
       <c r="H160" t="n">
-        <v>587193</v>
+        <v>50747000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B161" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C161"/>
+        <v>2019</v>
+      </c>
+      <c r="C161" t="n">
+        <v>79461</v>
+      </c>
       <c r="D161" t="n">
-        <v>11303</v>
+        <v>39731</v>
       </c>
       <c r="E161" t="n">
-        <v>93</v>
-      </c>
-      <c r="F161"/>
+        <v>24268</v>
+      </c>
+      <c r="F161" t="n">
+        <v>208382746</v>
+      </c>
       <c r="G161" t="n">
-        <v>39880458</v>
+        <v>104159149</v>
       </c>
       <c r="H161" t="n">
-        <v>611051</v>
+        <v>57171451</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B162" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C162"/>
+        <v>2020</v>
+      </c>
+      <c r="C162" t="n">
+        <v>90836</v>
+      </c>
       <c r="D162" t="n">
-        <v>8981</v>
+        <v>45418</v>
       </c>
       <c r="E162" t="n">
-        <v>1431</v>
-      </c>
-      <c r="F162"/>
+        <v>23936</v>
+      </c>
+      <c r="F162" t="n">
+        <v>242068825</v>
+      </c>
       <c r="G162" t="n">
-        <v>55032205</v>
+        <v>121240880</v>
       </c>
       <c r="H162" t="n">
-        <v>10345899</v>
+        <v>54554807</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B163" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C163"/>
+        <v>2021</v>
+      </c>
+      <c r="C163" t="n">
+        <v>39610</v>
+      </c>
       <c r="D163" t="n">
-        <v>9154</v>
+        <v>39610</v>
       </c>
       <c r="E163" t="n">
-        <v>1274</v>
-      </c>
-      <c r="F163"/>
+        <v>24288</v>
+      </c>
+      <c r="F163" t="n">
+        <v>123601642</v>
+      </c>
       <c r="G163" t="n">
-        <v>43024287</v>
+        <v>123529412</v>
       </c>
       <c r="H163" t="n">
-        <v>8713410</v>
+        <v>77883456</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B164" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C164"/>
+        <v>2022</v>
+      </c>
+      <c r="C164" t="n">
+        <v>42201</v>
+      </c>
       <c r="D164" t="n">
-        <v>1254</v>
+        <v>42201</v>
       </c>
       <c r="E164" t="n">
-        <v>121</v>
-      </c>
-      <c r="F164"/>
+        <v>19834</v>
+      </c>
+      <c r="F164" t="n">
+        <v>185828824</v>
+      </c>
       <c r="G164" t="n">
-        <v>5198254</v>
+        <v>185902438</v>
       </c>
       <c r="H164" t="n">
-        <v>336000</v>
+        <v>90333025</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B165" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C165"/>
+        <v>2023</v>
+      </c>
+      <c r="C165" t="n">
+        <v>40667</v>
+      </c>
       <c r="D165" t="n">
-        <v>1230</v>
+        <v>40667</v>
       </c>
       <c r="E165" t="n">
-        <v>230</v>
-      </c>
-      <c r="F165"/>
+        <v>21178</v>
+      </c>
+      <c r="F165" t="n">
+        <v>185888494</v>
+      </c>
       <c r="G165" t="n">
-        <v>5090588</v>
+        <v>185724551</v>
       </c>
       <c r="H165" t="n">
-        <v>559436</v>
+        <v>101582700</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B166" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C166"/>
-      <c r="D166" t="n">
-        <v>1169</v>
-      </c>
-      <c r="E166" t="n">
-        <v>324</v>
-      </c>
-      <c r="F166"/>
-      <c r="G166" t="n">
-        <v>4758884</v>
-      </c>
-      <c r="H166" t="n">
-        <v>543050</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C166" t="n">
+        <v>43554</v>
+      </c>
+      <c r="D166"/>
+      <c r="E166"/>
+      <c r="F166" t="n">
+        <v>181556855</v>
+      </c>
+      <c r="G166"/>
+      <c r="H166"/>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B167" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C167"/>
+        <v>2018</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1346</v>
+      </c>
       <c r="D167" t="n">
-        <v>1175</v>
+        <v>697</v>
       </c>
       <c r="E167" t="n">
-        <v>250</v>
-      </c>
-      <c r="F167"/>
+        <v>12</v>
+      </c>
+      <c r="F167" t="n">
+        <v>3884044</v>
+      </c>
       <c r="G167" t="n">
-        <v>5299821</v>
+        <v>2331632</v>
       </c>
       <c r="H167" t="n">
-        <v>643045</v>
+        <v>121000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B168" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C168"/>
+        <v>2019</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1365</v>
+      </c>
       <c r="D168" t="n">
-        <v>1022</v>
+        <v>665</v>
       </c>
       <c r="E168" t="n">
-        <v>222</v>
-      </c>
-      <c r="F168"/>
+        <v>1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>4590436</v>
+      </c>
       <c r="G168" t="n">
-        <v>5611221</v>
+        <v>2003450</v>
       </c>
       <c r="H168" t="n">
-        <v>731407</v>
+        <v>8870</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B169" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C169"/>
+        <v>2020</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1224</v>
+      </c>
       <c r="D169" t="n">
-        <v>832</v>
+        <v>914</v>
       </c>
       <c r="E169" t="n">
-        <v>215</v>
-      </c>
-      <c r="F169"/>
+        <v>0</v>
+      </c>
+      <c r="F169" t="n">
+        <v>4582608</v>
+      </c>
       <c r="G169" t="n">
-        <v>4549746</v>
+        <v>2685738</v>
       </c>
       <c r="H169" t="n">
-        <v>793390</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B170" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C170"/>
+        <v>2021</v>
+      </c>
+      <c r="C170" t="n">
+        <v>490</v>
+      </c>
       <c r="D170" t="n">
-        <v>2224</v>
+        <v>867</v>
       </c>
       <c r="E170" t="n">
-        <v>1233</v>
-      </c>
-      <c r="F170"/>
+        <v>0</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1411200</v>
+      </c>
       <c r="G170" t="n">
-        <v>5494052</v>
+        <v>4984835</v>
       </c>
       <c r="H170" t="n">
-        <v>2712000</v>
+        <v>838</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B171" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C171"/>
+        <v>2022</v>
+      </c>
+      <c r="C171" t="n">
+        <v>827</v>
+      </c>
       <c r="D171" t="n">
-        <v>2688</v>
+        <v>423</v>
       </c>
       <c r="E171" t="n">
-        <v>1739</v>
-      </c>
-      <c r="F171"/>
+        <v>0</v>
+      </c>
+      <c r="F171" t="n">
+        <v>2732993</v>
+      </c>
       <c r="G171" t="n">
-        <v>7191255</v>
+        <v>1398995</v>
       </c>
       <c r="H171" t="n">
-        <v>3993661</v>
+        <v>9418</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B172" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C172"/>
+        <v>2023</v>
+      </c>
+      <c r="C172" t="n">
+        <v>368</v>
+      </c>
       <c r="D172" t="n">
-        <v>2296</v>
+        <v>317</v>
       </c>
       <c r="E172" t="n">
-        <v>1466</v>
-      </c>
-      <c r="F172"/>
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1367528</v>
+      </c>
       <c r="G172" t="n">
-        <v>5616026</v>
+        <v>1184749</v>
       </c>
       <c r="H172" t="n">
-        <v>3351178</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B173" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C173"/>
-      <c r="D173" t="n">
-        <v>2514</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1140</v>
-      </c>
-      <c r="F173"/>
-      <c r="G173" t="n">
-        <v>7185568</v>
-      </c>
-      <c r="H173" t="n">
-        <v>2619337</v>
-      </c>
+        <v>2024</v>
+      </c>
+      <c r="C173" t="n">
+        <v>176</v>
+      </c>
+      <c r="D173"/>
+      <c r="E173"/>
+      <c r="F173" t="n">
+        <v>637242</v>
+      </c>
+      <c r="G173"/>
+      <c r="H173"/>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B174" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C174"/>
+        <v>2018</v>
+      </c>
+      <c r="C174" t="n">
+        <v>24597</v>
+      </c>
       <c r="D174" t="n">
-        <v>2614</v>
+        <v>12298</v>
       </c>
       <c r="E174" t="n">
-        <v>1631</v>
-      </c>
-      <c r="F174"/>
+        <v>9826</v>
+      </c>
+      <c r="F174" t="n">
+        <v>67115389</v>
+      </c>
       <c r="G174" t="n">
-        <v>7863883</v>
+        <v>30648544</v>
       </c>
       <c r="H174" t="n">
-        <v>4181815</v>
+        <v>24954000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B175" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C175"/>
+        <v>2019</v>
+      </c>
+      <c r="C175" t="n">
+        <v>25256</v>
+      </c>
       <c r="D175" t="n">
-        <v>2768</v>
+        <v>12848</v>
       </c>
       <c r="E175" t="n">
-        <v>1706</v>
-      </c>
-      <c r="F175"/>
+        <v>10091</v>
+      </c>
+      <c r="F175" t="n">
+        <v>74968917</v>
+      </c>
       <c r="G175" t="n">
-        <v>9705317</v>
+        <v>31861870</v>
       </c>
       <c r="H175" t="n">
-        <v>4792320</v>
+        <v>27861042</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B176" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C176"/>
-      <c r="D176"/>
+        <v>2020</v>
+      </c>
+      <c r="C176" t="n">
+        <v>24300</v>
+      </c>
+      <c r="D176" t="n">
+        <v>12371</v>
+      </c>
       <c r="E176" t="n">
-        <v>3</v>
-      </c>
-      <c r="F176"/>
-      <c r="G176"/>
+        <v>9442</v>
+      </c>
+      <c r="F176" t="n">
+        <v>77975735</v>
+      </c>
+      <c r="G176" t="n">
+        <v>39335532</v>
+      </c>
       <c r="H176" t="n">
-        <v>48000</v>
+        <v>27893432</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
+        <v>33</v>
+      </c>
+      <c r="B177" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C177" t="n">
+        <v>23428</v>
+      </c>
+      <c r="D177" t="n">
+        <v>11714</v>
+      </c>
+      <c r="E177" t="n">
+        <v>8967</v>
+      </c>
+      <c r="F177" t="n">
+        <v>71720005</v>
+      </c>
+      <c r="G177" t="n">
+        <v>36587679</v>
+      </c>
+      <c r="H177" t="n">
+        <v>24696739</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>33</v>
+      </c>
+      <c r="B178" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C178" t="n">
+        <v>22424</v>
+      </c>
+      <c r="D178" t="n">
+        <v>11211</v>
+      </c>
+      <c r="E178" t="n">
+        <v>8105</v>
+      </c>
+      <c r="F178" t="n">
+        <v>82403423</v>
+      </c>
+      <c r="G178" t="n">
+        <v>36065959</v>
+      </c>
+      <c r="H178" t="n">
+        <v>24820229</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>33</v>
+      </c>
+      <c r="B179" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C179" t="n">
+        <v>22524</v>
+      </c>
+      <c r="D179" t="n">
+        <v>11264</v>
+      </c>
+      <c r="E179" t="n">
+        <v>7735</v>
+      </c>
+      <c r="F179" t="n">
+        <v>95955284</v>
+      </c>
+      <c r="G179" t="n">
+        <v>37456631</v>
+      </c>
+      <c r="H179" t="n">
+        <v>26587640</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>33</v>
+      </c>
+      <c r="B180" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C180" t="n">
+        <v>20108</v>
+      </c>
+      <c r="D180"/>
+      <c r="E180"/>
+      <c r="F180" t="n">
+        <v>87586942</v>
+      </c>
+      <c r="G180"/>
+      <c r="H180"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>34</v>
+      </c>
+      <c r="B181" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C181" t="n">
+        <v>13630</v>
+      </c>
+      <c r="D181" t="n">
+        <v>8239</v>
+      </c>
+      <c r="E181" t="n">
+        <v>99</v>
+      </c>
+      <c r="F181" t="n">
+        <v>57240284</v>
+      </c>
+      <c r="G181" t="n">
+        <v>36117260</v>
+      </c>
+      <c r="H181" t="n">
+        <v>676000</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>34</v>
+      </c>
+      <c r="B182" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C182" t="n">
+        <v>13768</v>
+      </c>
+      <c r="D182" t="n">
+        <v>8084</v>
+      </c>
+      <c r="E182" t="n">
+        <v>163</v>
+      </c>
+      <c r="F182" t="n">
+        <v>44816274</v>
+      </c>
+      <c r="G182" t="n">
+        <v>28264134</v>
+      </c>
+      <c r="H182" t="n">
+        <v>920679</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>34</v>
+      </c>
+      <c r="B183" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C183" t="n">
+        <v>15078</v>
+      </c>
+      <c r="D183" t="n">
+        <v>8690</v>
+      </c>
+      <c r="E183" t="n">
+        <v>93</v>
+      </c>
+      <c r="F183" t="n">
+        <v>51052876</v>
+      </c>
+      <c r="G183" t="n">
+        <v>29684045</v>
+      </c>
+      <c r="H183" t="n">
+        <v>587193</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>34</v>
+      </c>
+      <c r="B184" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C184" t="n">
+        <v>22278</v>
+      </c>
+      <c r="D184" t="n">
+        <v>11303</v>
+      </c>
+      <c r="E184" t="n">
+        <v>93</v>
+      </c>
+      <c r="F184" t="n">
+        <v>611051</v>
+      </c>
+      <c r="G184" t="n">
+        <v>39880458</v>
+      </c>
+      <c r="H184" t="n">
+        <v>611051</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>34</v>
+      </c>
+      <c r="B185" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" t="n">
+        <v>8981</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1431</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>55032205</v>
+      </c>
+      <c r="H185" t="n">
+        <v>10345899</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>34</v>
+      </c>
+      <c r="B186" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C186" t="n">
+        <v>52</v>
+      </c>
+      <c r="D186" t="n">
+        <v>9154</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1274</v>
+      </c>
+      <c r="F186" t="n">
+        <v>511900</v>
+      </c>
+      <c r="G186" t="n">
+        <v>43024287</v>
+      </c>
+      <c r="H186" t="n">
+        <v>8713410</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>34</v>
+      </c>
+      <c r="B187" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C187" t="n">
+        <v>8176</v>
+      </c>
+      <c r="D187"/>
+      <c r="E187"/>
+      <c r="F187" t="n">
+        <v>40125428</v>
+      </c>
+      <c r="G187"/>
+      <c r="H187"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>35</v>
+      </c>
+      <c r="B188" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1254</v>
+      </c>
+      <c r="E188" t="n">
+        <v>121</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>5198254</v>
+      </c>
+      <c r="H188" t="n">
+        <v>336000</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>35</v>
+      </c>
+      <c r="B189" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1230</v>
+      </c>
+      <c r="E189" t="n">
+        <v>230</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>5090588</v>
+      </c>
+      <c r="H189" t="n">
+        <v>559436</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>35</v>
+      </c>
+      <c r="B190" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2334</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1169</v>
+      </c>
+      <c r="E190" t="n">
+        <v>324</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>4758884</v>
+      </c>
+      <c r="H190" t="n">
+        <v>543050</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>35</v>
+      </c>
+      <c r="B191" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2362</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1175</v>
+      </c>
+      <c r="E191" t="n">
+        <v>250</v>
+      </c>
+      <c r="F191" t="n">
+        <v>10701636</v>
+      </c>
+      <c r="G191" t="n">
+        <v>5299821</v>
+      </c>
+      <c r="H191" t="n">
+        <v>643045</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>35</v>
+      </c>
+      <c r="B192" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C192" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E192" t="n">
+        <v>222</v>
+      </c>
+      <c r="F192" t="n">
+        <v>5675187</v>
+      </c>
+      <c r="G192" t="n">
+        <v>5611221</v>
+      </c>
+      <c r="H192" t="n">
+        <v>731407</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>35</v>
+      </c>
+      <c r="B193" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C193" t="n">
+        <v>587</v>
+      </c>
+      <c r="D193" t="n">
+        <v>832</v>
+      </c>
+      <c r="E193" t="n">
+        <v>215</v>
+      </c>
+      <c r="F193" t="n">
+        <v>3368603</v>
+      </c>
+      <c r="G193" t="n">
+        <v>4549746</v>
+      </c>
+      <c r="H193" t="n">
+        <v>793390</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>35</v>
+      </c>
+      <c r="B194" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C194" t="n">
+        <v>1747</v>
+      </c>
+      <c r="D194"/>
+      <c r="E194"/>
+      <c r="F194" t="n">
+        <v>9072746</v>
+      </c>
+      <c r="G194"/>
+      <c r="H194"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>36</v>
+      </c>
+      <c r="B195" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C195" t="n">
+        <v>4494</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2224</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1233</v>
+      </c>
+      <c r="F195" t="n">
+        <v>11045606</v>
+      </c>
+      <c r="G195" t="n">
+        <v>5494052</v>
+      </c>
+      <c r="H195" t="n">
+        <v>2712000</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>36</v>
+      </c>
+      <c r="B196" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C196" t="n">
+        <v>5377</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2688</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1739</v>
+      </c>
+      <c r="F196" t="n">
+        <v>14199868</v>
+      </c>
+      <c r="G196" t="n">
+        <v>7191255</v>
+      </c>
+      <c r="H196" t="n">
+        <v>3993661</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>36</v>
+      </c>
+      <c r="B197" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C197" t="n">
+        <v>4303</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2296</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1466</v>
+      </c>
+      <c r="F197" t="n">
+        <v>10992211</v>
+      </c>
+      <c r="G197" t="n">
+        <v>5616026</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3351178</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>36</v>
+      </c>
+      <c r="B198" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C198" t="n">
+        <v>4835</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2514</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1140</v>
+      </c>
+      <c r="F198" t="n">
+        <v>13981799</v>
+      </c>
+      <c r="G198" t="n">
+        <v>7185568</v>
+      </c>
+      <c r="H198" t="n">
+        <v>2619337</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>36</v>
+      </c>
+      <c r="B199" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C199" t="n">
+        <v>5362</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2614</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1631</v>
+      </c>
+      <c r="F199" t="n">
+        <v>16122503</v>
+      </c>
+      <c r="G199" t="n">
+        <v>7863883</v>
+      </c>
+      <c r="H199" t="n">
+        <v>4181815</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>36</v>
+      </c>
+      <c r="B200" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C200" t="n">
+        <v>5536</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2768</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1706</v>
+      </c>
+      <c r="F200" t="n">
+        <v>17908327</v>
+      </c>
+      <c r="G200" t="n">
+        <v>9705317</v>
+      </c>
+      <c r="H200" t="n">
+        <v>4792320</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>36</v>
+      </c>
+      <c r="B201" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C201" t="n">
+        <v>5137</v>
+      </c>
+      <c r="D201"/>
+      <c r="E201"/>
+      <c r="F201" t="n">
+        <v>18298031</v>
+      </c>
+      <c r="G201"/>
+      <c r="H201"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
         <v>37</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B202" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C202" t="n">
+        <v>17485</v>
+      </c>
+      <c r="D202"/>
+      <c r="E202" t="n">
+        <v>3</v>
+      </c>
+      <c r="F202" t="n">
+        <v>66287249</v>
+      </c>
+      <c r="G202"/>
+      <c r="H202" t="n">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>37</v>
+      </c>
+      <c r="B203" t="n">
         <v>2019</v>
       </c>
-      <c r="C177"/>
-      <c r="D177"/>
-      <c r="E177" t="n">
+      <c r="C203"/>
+      <c r="D203"/>
+      <c r="E203" t="n">
         <v>240</v>
       </c>
-      <c r="F177"/>
-      <c r="G177"/>
-      <c r="H177" t="n">
+      <c r="F203"/>
+      <c r="G203"/>
+      <c r="H203" t="n">
         <v>4196318</v>
       </c>
     </row>

--- a/output/freshwater/Europe_freshwater_summary_latest.xlsx
+++ b/output/freshwater/Europe_freshwater_summary_latest.xlsx
@@ -4780,7 +4780,7 @@
         <v>2021</v>
       </c>
       <c r="C184" t="n">
-        <v>22278</v>
+        <v>445</v>
       </c>
       <c r="D184" t="n">
         <v>11303</v>
@@ -4789,7 +4789,7 @@
         <v>93</v>
       </c>
       <c r="F184" t="n">
-        <v>611051</v>
+        <v>2961228</v>
       </c>
       <c r="G184" t="n">
         <v>39880458</v>
@@ -4806,7 +4806,7 @@
         <v>2022</v>
       </c>
       <c r="C185" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="D185" t="n">
         <v>8981</v>
@@ -4815,7 +4815,7 @@
         <v>1431</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>3019676</v>
       </c>
       <c r="G185" t="n">
         <v>55032205</v>
@@ -4832,7 +4832,7 @@
         <v>2023</v>
       </c>
       <c r="C186" t="n">
-        <v>52</v>
+        <v>548</v>
       </c>
       <c r="D186" t="n">
         <v>9154</v>
@@ -4841,7 +4841,7 @@
         <v>1274</v>
       </c>
       <c r="F186" t="n">
-        <v>511900</v>
+        <v>3113485</v>
       </c>
       <c r="G186" t="n">
         <v>43024287</v>
@@ -4858,12 +4858,12 @@
         <v>2024</v>
       </c>
       <c r="C187" t="n">
-        <v>8176</v>
+        <v>745</v>
       </c>
       <c r="D187"/>
       <c r="E187"/>
       <c r="F187" t="n">
-        <v>40125428</v>
+        <v>4003542</v>
       </c>
       <c r="G187"/>
       <c r="H187"/>
